--- a/src/attributions/attributions_saliency_traj_33.xlsx
+++ b/src/attributions/attributions_saliency_traj_33.xlsx
@@ -999,1709 +999,1709 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01095679402351379</v>
+        <v>2.393997965555172e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03577867150306702</v>
+        <v>0.0001117711290135048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0292254276573658</v>
+        <v>1.449560659239069e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005867911502718925</v>
+        <v>5.558870179811493e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06261011958122253</v>
+        <v>8.943451575760264e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07991926372051239</v>
+        <v>0.0001208044850500301</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01641571335494518</v>
+        <v>9.279058303945931e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02054471336305141</v>
+        <v>2.348783345951233e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.041329525411129</v>
+        <v>2.432754399706027e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02709013037383556</v>
+        <v>5.836834316141903e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02237716689705849</v>
+        <v>0.0001241284771822393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03540635854005814</v>
+        <v>2.907182897615712e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04948302358388901</v>
+        <v>7.824135536793619e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008149249479174614</v>
+        <v>6.139251490822062e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06496786326169968</v>
+        <v>0.0001263032609131187</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01081538386642933</v>
+        <v>1.19733413157519e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007374020293354988</v>
+        <v>1.436359343642835e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001653993036597967</v>
+        <v>1.283659821638139e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008009469136595726</v>
+        <v>1.384007373417262e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001746650785207748</v>
+        <v>2.448474697303027e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0160519927740097</v>
+        <v>1.486980727349874e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004252014681696892</v>
+        <v>3.519685378705617e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0006807160098105669</v>
+        <v>1.303254975937307e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03672782704234123</v>
+        <v>7.274178642546758e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03192805498838425</v>
+        <v>5.50500499230111e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008041856810450554</v>
+        <v>1.454662196920253e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004766769241541624</v>
+        <v>3.8218536246859e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01704642735421658</v>
+        <v>5.532770956051536e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05420944094657898</v>
+        <v>2.572903213149402e-06</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.04770781099796295</v>
+        <v>1.142196742875967e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.003554819617420435</v>
+        <v>1.941405389516149e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.02804499305784702</v>
+        <v>3.016121263499372e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01781601272523403</v>
+        <v>8.051689292187802e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01103188470005989</v>
+        <v>1.720858563203365e-05</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.03474609181284904</v>
+        <v>3.891489177476615e-05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.05906245857477188</v>
+        <v>7.596490831929259e-06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.001258810749277472</v>
+        <v>1.462110594729893e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.007545051630586386</v>
+        <v>2.764751661743503e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0009325755527243018</v>
+        <v>7.707306394877378e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02461200766265392</v>
+        <v>9.229308489011601e-06</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.005879399832338095</v>
+        <v>2.825392948579974e-05</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.009717241860926151</v>
+        <v>1.639755464566406e-05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00027035444509238</v>
+        <v>8.953450560511556e-06</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.009844901040196419</v>
+        <v>1.91744948097039e-05</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.02295324020087719</v>
+        <v>1.453261575079523e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01900083944201469</v>
+        <v>5.054509074398084e-06</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.03198236599564552</v>
+        <v>0.0001091000012820587</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.02057813853025436</v>
+        <v>1.675773819442838e-05</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.03264712914824486</v>
+        <v>1.891037391033024e-05</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02767831087112427</v>
+        <v>9.691592822491657e-06</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.08061453700065613</v>
+        <v>6.255518383113667e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.02347330190241337</v>
+        <v>2.921263785538031e-06</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.005807396024465561</v>
+        <v>9.104775926971342e-06</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.02169018238782883</v>
+        <v>5.408795004768763e-06</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.009395658038556576</v>
+        <v>2.039597166003659e-05</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.01857315003871918</v>
+        <v>1.920902468555141e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.01561573147773743</v>
+        <v>1.834324211813509e-05</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.03368394076824188</v>
+        <v>3.5632292565424e-05</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01535382680594921</v>
+        <v>8.001328751561232e-06</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.003480846062302589</v>
+        <v>2.105018575093709e-05</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02450475096702576</v>
+        <v>2.259229586343281e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01157858036458492</v>
+        <v>1.220239710164606e-06</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.03122793510556221</v>
+        <v>4.316034392104484e-06</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.02033190429210663</v>
+        <v>5.101741407997906e-06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0113674970343709</v>
+        <v>1.544896986160893e-05</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.002474738284945488</v>
+        <v>3.407207714190008e-06</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.003852605819702148</v>
+        <v>4.438926225702744e-06</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.004814473446458578</v>
+        <v>2.057792153209448e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.02991381660103798</v>
+        <v>1.422871173417661e-05</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01196870859712362</v>
+        <v>2.216109714936465e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.02982470020651817</v>
+        <v>6.823529020039132e-06</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05013349279761314</v>
+        <v>1.054554468282731e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.01549262925982475</v>
+        <v>2.123913873219863e-05</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0148520665243268</v>
+        <v>7.77538662077859e-05</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.02947318740189075</v>
+        <v>3.287222170911264e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.009140854701399803</v>
+        <v>1.601815529284067e-05</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03334052488207817</v>
+        <v>1.621885712665971e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.04905537515878677</v>
+        <v>4.509866994339973e-05</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0265604741871357</v>
+        <v>1.220089234266197e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.008472810499370098</v>
+        <v>3.279072643636027e-06</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.006526710465550423</v>
+        <v>1.09425936898333e-05</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0008774132002145052</v>
+        <v>2.11991118703736e-06</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.009008255787193775</v>
+        <v>3.239549550926313e-05</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0005217620637267828</v>
+        <v>1.286946371692466e-06</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01825621351599693</v>
+        <v>1.604910721653141e-06</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0005115445237606764</v>
+        <v>5.53094696442713e-06</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0196127574890852</v>
+        <v>2.875336213037372e-05</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.01078311912715435</v>
+        <v>1.787038286238385e-06</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0159035250544548</v>
+        <v>1.501527890468424e-06</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0114078875631094</v>
+        <v>5.825439529871801e-06</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.01302266400307417</v>
+        <v>2.761678297247272e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01054788567125797</v>
+        <v>3.304224810563028e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0007348543731495738</v>
+        <v>2.22220642172033e-05</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0238342359662056</v>
+        <v>5.226288067206042e-06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05810925364494324</v>
+        <v>1.665444688114803e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.02800356969237328</v>
+        <v>1.026879090204602e-05</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.02217445150017738</v>
+        <v>2.916422999987844e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.008862541988492012</v>
+        <v>1.184020584332757e-05</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.006618418730795383</v>
+        <v>8.885225724952761e-06</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.003844052087515593</v>
+        <v>8.12411690276349e-06</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.008026574738323689</v>
+        <v>3.273440961493179e-05</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.008110977709293365</v>
+        <v>3.010042291862192e-06</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.01561142690479755</v>
+        <v>4.198258466203697e-06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.009486372582614422</v>
+        <v>5.590491127804853e-07</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.01529684755951166</v>
+        <v>3.084454510826617e-05</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0146812591701746</v>
+        <v>2.284908759975224e-07</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0169157050549984</v>
+        <v>3.314509910978813e-07</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0118037536740303</v>
+        <v>4.199738214083482e-06</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.01426995731890202</v>
+        <v>4.481599171413109e-05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.001353949774056673</v>
+        <v>3.508432200760581e-05</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.00354818208143115</v>
+        <v>5.46503288205713e-05</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01765233278274536</v>
+        <v>2.559945642133243e-07</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03953498229384422</v>
+        <v>4.212899875710718e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.08249630033969879</v>
+        <v>5.540830534300767e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.02411885932087898</v>
+        <v>4.003256435680669e-06</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.05675169825553894</v>
+        <v>1.944982068380341e-05</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.02477339282631874</v>
+        <v>1.19046535473899e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.001832982525229454</v>
+        <v>1.41144869303389e-06</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.003397272899746895</v>
+        <v>3.061578172491863e-05</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.01685234904289246</v>
+        <v>8.060626896622125e-06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>6.80508092045784e-05</v>
+        <v>1.306832655245671e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0001741488958941773</v>
+        <v>3.091529379162239e-06</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0155769819393754</v>
+        <v>2.125060564139858e-05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.02067207172513008</v>
+        <v>5.968829555058619e-06</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.01762408763170242</v>
+        <v>1.578723640704993e-07</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0180056206882</v>
+        <v>3.574843958631391e-06</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.003158553503453732</v>
+        <v>1.836489718698431e-05</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.01221251673996449</v>
+        <v>1.593562501511769e-06</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.01412533409893513</v>
+        <v>2.600237166916486e-06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.006119402591139078</v>
+        <v>3.807511120612617e-06</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.009531843475997448</v>
+        <v>4.312203145673266e-07</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.003336624940857291</v>
+        <v>2.885721551137976e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01696959882974625</v>
+        <v>2.219786665591528e-06</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.03749766945838928</v>
+        <v>5.003389105695533e-06</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0005115612875670195</v>
+        <v>2.134899477823637e-05</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0008872980251908302</v>
+        <v>4.401616024551913e-06</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.002242280635982752</v>
+        <v>1.310259176534601e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.007243954576551914</v>
+        <v>3.188777100149309e-06</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.03254276514053345</v>
+        <v>1.478043213865021e-05</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.002900541760027409</v>
+        <v>3.909392944478896e-06</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01462858263403177</v>
+        <v>2.280941953358706e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001149596646428108</v>
+        <v>4.659746991819702e-06</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.03286509588360786</v>
+        <v>2.689523626031587e-08</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.005559427663683891</v>
+        <v>6.827519428043161e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.004543880932033062</v>
+        <v>5.113199676998192e-07</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.00671773124486208</v>
+        <v>2.984878665301949e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.005542119033634663</v>
+        <v>3.37354890689312e-06</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.005043867975473404</v>
+        <v>2.990295342897298e-06</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.008742440491914749</v>
+        <v>2.376644260948524e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.007796095684170723</v>
+        <v>7.066418220347259e-06</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002023478969931602</v>
+        <v>1.167302707472118e-05</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.00426182197406888</v>
+        <v>1.274711758014746e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01588064804673195</v>
+        <v>5.214743850956438e-06</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.003570473520085216</v>
+        <v>2.483702473909943e-06</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.007214107550680637</v>
+        <v>3.432632729527541e-05</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.002619455568492413</v>
+        <v>6.45523186904029e-07</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01811730116605759</v>
+        <v>3.71712417290837e-06</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.006331661716103554</v>
+        <v>9.876184776658192e-06</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.009881297126412392</v>
+        <v>2.665427200554404e-05</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.009594307281076908</v>
+        <v>1.71754504663113e-06</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0128107275813818</v>
+        <v>1.268253981834278e-07</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.01122910156846046</v>
+        <v>3.826920647043153e-07</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01347066089510918</v>
+        <v>1.187317593576154e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002956351265311241</v>
+        <v>1.348135265288875e-05</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.002800552872940898</v>
+        <v>1.403056830895366e-05</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.02738797664642334</v>
+        <v>8.083035936579108e-06</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.03949366137385368</v>
+        <v>1.101414454751648e-05</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.008224276825785637</v>
+        <v>1.963527756743133e-05</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.01238643657416105</v>
+        <v>5.104463525640313e-06</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.01536157075315714</v>
+        <v>1.606614887350588e-06</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.01024219114333391</v>
+        <v>2.020306237682234e-05</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.01413110550493002</v>
+        <v>1.912353036459535e-05</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01658330298960209</v>
+        <v>2.529356243030634e-05</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.03802637383341789</v>
+        <v>1.334042099188082e-05</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01024717092514038</v>
+        <v>6.112469418440014e-05</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.03918606415390968</v>
+        <v>3.000336982950103e-05</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.009875387884676456</v>
+        <v>2.544994458730798e-05</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.00654557254165411</v>
+        <v>1.542043537483551e-05</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.04187164828181267</v>
+        <v>1.32090326587786e-05</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.03398056328296661</v>
+        <v>8.88132126419805e-06</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.005429152399301529</v>
+        <v>1.300154872296844e-05</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.008791390806436539</v>
+        <v>1.068113579094643e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.01429909002035856</v>
+        <v>1.398836502630729e-06</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.004252444952726364</v>
+        <v>2.209004742326215e-05</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.03132285177707672</v>
+        <v>1.867854007286951e-05</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.01440815348178148</v>
+        <v>3.155591548420489e-05</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.01760094426572323</v>
+        <v>1.174567205453059e-05</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.05144480988383293</v>
+        <v>2.232379529232276e-06</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0267484039068222</v>
+        <v>3.396196461835643e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.5990822147578e-06</v>
+        <v>0.0006985715008340776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001241068355739117</v>
+        <v>0.004783905111253262</v>
       </c>
       <c r="C3" t="n">
-        <v>3.302412005723454e-05</v>
+        <v>0.0007079992210492492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007062787190079689</v>
+        <v>0.00390542228706181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003131868143100291</v>
+        <v>0.0002619958249852061</v>
       </c>
       <c r="F3" t="n">
-        <v>4.461344360606745e-05</v>
+        <v>0.002274590544402599</v>
       </c>
       <c r="G3" t="n">
-        <v>2.287029201397672e-05</v>
+        <v>0.00148986408021301</v>
       </c>
       <c r="H3" t="n">
-        <v>3.045486846531276e-05</v>
+        <v>0.0005014710477553308</v>
       </c>
       <c r="I3" t="n">
-        <v>8.965312736108899e-05</v>
+        <v>0.0003855244722217321</v>
       </c>
       <c r="J3" t="n">
-        <v>8.275111758848652e-05</v>
+        <v>0.0007160554523579776</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001099531073123217</v>
+        <v>0.005439102649688721</v>
       </c>
       <c r="L3" t="n">
-        <v>1.350029015156906e-05</v>
+        <v>0.001239554607309401</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000567221490200609</v>
+        <v>0.005362494848668575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001791787071852013</v>
+        <v>0.0004296619445085526</v>
       </c>
       <c r="O3" t="n">
-        <v>3.441918670432642e-05</v>
+        <v>0.001674616476520896</v>
       </c>
       <c r="P3" t="n">
-        <v>4.89383382955566e-05</v>
+        <v>0.0007303323363885283</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001479544007452205</v>
+        <v>0.002074634889140725</v>
       </c>
       <c r="R3" t="n">
-        <v>6.022040179232135e-05</v>
+        <v>0.0003697322681546211</v>
       </c>
       <c r="S3" t="n">
-        <v>5.191530726733617e-05</v>
+        <v>0.0004523474199231714</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002426589780952781</v>
+        <v>0.000384212878998369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001017919057630934</v>
+        <v>0.0001896688045235351</v>
       </c>
       <c r="V3" t="n">
-        <v>9.43051854846999e-05</v>
+        <v>0.0002095605013892055</v>
       </c>
       <c r="W3" t="n">
-        <v>2.011293690884486e-05</v>
+        <v>0.0003139611799269915</v>
       </c>
       <c r="X3" t="n">
-        <v>4.547834396362305e-05</v>
+        <v>0.001580476993694901</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.985511516977567e-06</v>
+        <v>2.96245125355199e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001263715676032007</v>
+        <v>0.0003461085143499076</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001280193391721696</v>
+        <v>0.0006423265440389514</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001303149765590206</v>
+        <v>2.628379297675565e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.588467219145969e-05</v>
+        <v>0.0003863834426738322</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.553739977884106e-05</v>
+        <v>3.86120518669486e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.322001667693257e-05</v>
+        <v>0.0008035075152292848</v>
       </c>
       <c r="AF3" t="n">
-        <v>4.185264697298408e-05</v>
+        <v>0.0002217593428213149</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.540144800557755e-05</v>
+        <v>0.000117139657959342</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.41195625171531e-05</v>
+        <v>0.0003278918156865984</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.854216215084307e-05</v>
+        <v>0.0001742757158353925</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6.69011496938765e-05</v>
+        <v>0.0004001299967058003</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.052372267120518e-05</v>
+        <v>0.000288988696411252</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0002019720850512385</v>
+        <v>0.0011153673985973</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.198315946268849e-05</v>
+        <v>7.953141175676137e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.011154957581311e-05</v>
+        <v>0.0005333648296073079</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.631271283666138e-07</v>
+        <v>0.00149885262362659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001904249656945467</v>
+        <v>0.001108776312321424</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.858161860785913e-05</v>
+        <v>0.0002892945485655218</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.406234852969646e-05</v>
+        <v>0.0003359866968821734</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.528059359174222e-05</v>
+        <v>6.472974200733006e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0001648710604058579</v>
+        <v>0.0001955238985829055</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0007136754575185478</v>
+        <v>0.003641940653324127</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0001150290190707892</v>
+        <v>0.0003284323029220104</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0002266531373606995</v>
+        <v>0.001894349814392626</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.248411515727639e-06</v>
+        <v>8.295872248709202e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.424763781367801e-05</v>
+        <v>1.941039226949215e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.499944275768939e-05</v>
+        <v>0.0002573730307631195</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0002391722082393244</v>
+        <v>0.0002413163892924786</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.313510751468129e-05</v>
+        <v>0.0005938101094216108</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.312148666940629e-05</v>
+        <v>0.0007335540722124279</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0001990299642784521</v>
+        <v>0.0001138585794251412</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0001149636445916258</v>
+        <v>0.00115155428647995</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0002196917484980077</v>
+        <v>0.0002271377452416345</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.000419061747379601</v>
+        <v>0.0003459077852312475</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0001798294397303835</v>
+        <v>0.001773572526872158</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.487298479536548e-05</v>
+        <v>0.0003478160942904651</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0001534279290353879</v>
+        <v>0.0003246400156058371</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.358948015375063e-05</v>
+        <v>0.001089136814698577</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002546451869420707</v>
+        <v>0.0003487266367301345</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.962356125470251e-05</v>
+        <v>0.0004880953347310424</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0001068988349288702</v>
+        <v>0.0001085735420929268</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.231334969517775e-05</v>
+        <v>0.0004132002941332757</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0002035822253674269</v>
+        <v>0.0003720516397152096</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001381843030685559</v>
+        <v>0.0002070523914881051</v>
       </c>
       <c r="BR3" t="n">
-        <v>8.524411532562226e-05</v>
+        <v>0.0007111604209057987</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.832555613480508e-05</v>
+        <v>0.0005264710052870214</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.935303827049211e-05</v>
+        <v>0.0001102520836866461</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0001451417483622208</v>
+        <v>0.0003523578634485602</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0003486472996883094</v>
+        <v>0.002492485335096717</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.175954124249984e-07</v>
+        <v>0.0002860962122213095</v>
       </c>
       <c r="BX3" t="n">
-        <v>5.589751526713371e-05</v>
+        <v>0.001485479529947042</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0001917733170557767</v>
+        <v>0.0004328842333052307</v>
       </c>
       <c r="BZ3" t="n">
-        <v>5.001885438105091e-05</v>
+        <v>0.0009669061400927603</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.117065039579757e-05</v>
+        <v>7.470829586964101e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>7.393571286229417e-05</v>
+        <v>0.0001270837237825617</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.365362888667732e-05</v>
+        <v>0.0004470270359888673</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.188295861240476e-07</v>
+        <v>0.0001917348999995738</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.000188296617125161</v>
+        <v>0.001450009294785559</v>
       </c>
       <c r="CF3" t="n">
-        <v>1.243787210114533e-05</v>
+        <v>0.0002010681928368285</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.000146361708175391</v>
+        <v>0.001082561793737113</v>
       </c>
       <c r="CH3" t="n">
-        <v>3.777497113333084e-05</v>
+        <v>0.0004413493152242154</v>
       </c>
       <c r="CI3" t="n">
-        <v>3.471016043476993e-06</v>
+        <v>3.819511039182544e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>4.24155659857206e-05</v>
+        <v>0.0001232831855304539</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.672236794547644e-05</v>
+        <v>1.008388517220737e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.361258339078631e-05</v>
+        <v>0.0003417653497308493</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0002032208722084761</v>
+        <v>0.0007391809485852718</v>
       </c>
       <c r="CN3" t="n">
-        <v>5.509159564098809e-06</v>
+        <v>0.00177278439514339</v>
       </c>
       <c r="CO3" t="n">
-        <v>7.711804937571287e-05</v>
+        <v>0.0008102089050225914</v>
       </c>
       <c r="CP3" t="n">
-        <v>5.660382157657295e-05</v>
+        <v>0.0008388065034523606</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0001640269183553755</v>
+        <v>0.002056030090898275</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.000256143364822492</v>
+        <v>0.0001306212943745777</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0001533984614070505</v>
+        <v>0.0008977294201031327</v>
       </c>
       <c r="CT3" t="n">
-        <v>4.251143764122389e-05</v>
+        <v>0.0004414675058797002</v>
       </c>
       <c r="CU3" t="n">
-        <v>2.67059585894458e-05</v>
+        <v>0.0008114404627121985</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.457406142435502e-05</v>
+        <v>0.0003251117013860494</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0002061783743556589</v>
+        <v>0.001495142467319965</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.28496349134366e-05</v>
+        <v>0.000165217585163191</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0001631999184610322</v>
+        <v>0.001135120517574251</v>
       </c>
       <c r="CZ3" t="n">
-        <v>5.600148597295629e-06</v>
+        <v>0.0002919500111602247</v>
       </c>
       <c r="DA3" t="n">
-        <v>4.397819429868832e-05</v>
+        <v>8.683356281835586e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>6.782580749131739e-05</v>
+        <v>8.206663187593222e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.185057863040129e-05</v>
+        <v>7.930728315841407e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.367526758462191e-05</v>
+        <v>0.0004083355888724327</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0001690929930191487</v>
+        <v>0.001188820577226579</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0003952911647502333</v>
+        <v>0.001316390698775649</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001111848905566148</v>
+        <v>0.0005159715074114501</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0003072451800107956</v>
+        <v>0.001255624927580357</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.005080336355604e-05</v>
+        <v>0.001119218184612691</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0001171392796095461</v>
+        <v>0.00127215392421931</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.350550393108279e-06</v>
+        <v>0.0003328758175484836</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001177307858597487</v>
+        <v>0.002022344619035721</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.598263224877883e-05</v>
+        <v>0.0007366501376964152</v>
       </c>
       <c r="DN3" t="n">
-        <v>8.361911750398576e-05</v>
+        <v>0.0002004246198339388</v>
       </c>
       <c r="DO3" t="n">
-        <v>9.041088924277574e-05</v>
+        <v>0.001332185347564518</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0001175189245259389</v>
+        <v>0.0002257694723084569</v>
       </c>
       <c r="DQ3" t="n">
-        <v>4.278305277694017e-05</v>
+        <v>0.0007591457106173038</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.221909042214975e-05</v>
+        <v>0.0003309337480459362</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.0001058929046848789</v>
+        <v>0.0006682448438368738</v>
       </c>
       <c r="DT3" t="n">
-        <v>7.169539458118379e-05</v>
+        <v>0.0002644263731781393</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.867432527244091e-05</v>
+        <v>0.0003009583160746843</v>
       </c>
       <c r="DV3" t="n">
-        <v>9.916462295223027e-05</v>
+        <v>0.001357414294034243</v>
       </c>
       <c r="DW3" t="n">
-        <v>6.284001574385911e-05</v>
+        <v>6.224199751159176e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0001367282820865512</v>
+        <v>0.0001866534003056586</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0001285523467231542</v>
+        <v>0.0003742416447494179</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001299738796660677</v>
+        <v>0.000748117221519351</v>
       </c>
       <c r="EA3" t="n">
-        <v>4.586087379720993e-05</v>
+        <v>0.0001312086533289403</v>
       </c>
       <c r="EB3" t="n">
-        <v>5.322629294823855e-05</v>
+        <v>0.0006375499651767313</v>
       </c>
       <c r="EC3" t="n">
-        <v>5.358337875804864e-05</v>
+        <v>2.754543129412923e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>9.81976481853053e-05</v>
+        <v>0.001595601788721979</v>
       </c>
       <c r="EE3" t="n">
-        <v>9.02451720321551e-05</v>
+        <v>0.00168947596102953</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0001405243965564296</v>
+        <v>0.0001738756109261885</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0002229041274404153</v>
+        <v>0.0007453890284523368</v>
       </c>
       <c r="EH3" t="n">
-        <v>4.771256499225274e-05</v>
+        <v>0.0002750075072981417</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0001026487952913158</v>
+        <v>0.0007494786405004561</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.000109521541162394</v>
+        <v>0.0001333830878138542</v>
       </c>
       <c r="EK3" t="n">
-        <v>1.735680780257098e-05</v>
+        <v>0.0001401911868015304</v>
       </c>
       <c r="EL3" t="n">
-        <v>2.820325244101696e-05</v>
+        <v>0.0001489527785452083</v>
       </c>
       <c r="EM3" t="n">
-        <v>4.557464490062557e-05</v>
+        <v>8.823259850032628e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>2.726285674725659e-05</v>
+        <v>0.0002544122689869255</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.293097557208966e-05</v>
+        <v>0.0005168947973288596</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0002037071826634929</v>
+        <v>0.0007273070514202118</v>
       </c>
       <c r="EQ3" t="n">
-        <v>9.436167601961643e-05</v>
+        <v>0.0004191255429759622</v>
       </c>
       <c r="ER3" t="n">
-        <v>5.060737385065295e-05</v>
+        <v>0.0005930050974711776</v>
       </c>
       <c r="ES3" t="n">
-        <v>3.120379460597178e-06</v>
+        <v>0.000385584426112473</v>
       </c>
       <c r="ET3" t="n">
-        <v>5.550638161366805e-05</v>
+        <v>0.001003095298074186</v>
       </c>
       <c r="EU3" t="n">
-        <v>2.499606307537761e-05</v>
+        <v>0.000575660786125809</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.540512130304705e-05</v>
+        <v>0.0001627519086468965</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0001062229493982159</v>
+        <v>0.0005875069182366133</v>
       </c>
       <c r="EX3" t="n">
-        <v>6.897898856550455e-07</v>
+        <v>0.0001196644880110398</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0002296302700415254</v>
+        <v>0.001613420550711453</v>
       </c>
       <c r="EZ3" t="n">
-        <v>6.86866087562521e-06</v>
+        <v>7.221024134196341e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0001293695095228031</v>
+        <v>0.00124108069576323</v>
       </c>
       <c r="FB3" t="n">
-        <v>1.733534372760914e-05</v>
+        <v>0.0004736162081826478</v>
       </c>
       <c r="FC3" t="n">
-        <v>5.358564158086665e-05</v>
+        <v>0.0002719614421948791</v>
       </c>
       <c r="FD3" t="n">
-        <v>4.658033140003681e-05</v>
+        <v>0.0002331686991965398</v>
       </c>
       <c r="FE3" t="n">
-        <v>8.580115718359593e-06</v>
+        <v>0.0001760597369866446</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.485303230059799e-05</v>
+        <v>0.0003724058624356985</v>
       </c>
       <c r="FG3" t="n">
-        <v>1.625794357096311e-05</v>
+        <v>0.0003988367388956249</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0001411539415130392</v>
+        <v>0.0007102168165147305</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.000104154423752334</v>
+        <v>0.0007305287290364504</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.0001190112379845232</v>
+        <v>0.0001667620963416994</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.000142634758958593</v>
+        <v>0.000480957911349833</v>
       </c>
       <c r="FL3" t="n">
-        <v>6.304000999080017e-05</v>
+        <v>0.0003722297842614353</v>
       </c>
       <c r="FM3" t="n">
-        <v>2.892107659135945e-05</v>
+        <v>0.0001728485221974552</v>
       </c>
       <c r="FN3" t="n">
-        <v>5.796440746053122e-06</v>
+        <v>0.0002747785474639386</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.486757355451118e-05</v>
+        <v>0.0006775522488169372</v>
       </c>
       <c r="FP3" t="n">
-        <v>6.354468496283516e-05</v>
+        <v>0.0002426037972327322</v>
       </c>
       <c r="FQ3" t="n">
-        <v>8.132860239129514e-05</v>
+        <v>0.0006526407087221742</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0003326484293211251</v>
+        <v>0.0001016878013615496</v>
       </c>
       <c r="FS3" t="n">
-        <v>9.530191164230928e-05</v>
+        <v>0.001993835438042879</v>
       </c>
       <c r="FT3" t="n">
-        <v>3.201651270501316e-05</v>
+        <v>0.001095920219086111</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0001517660130048171</v>
+        <v>0.0009871774818748236</v>
       </c>
       <c r="FV3" t="n">
-        <v>2.759998278634157e-05</v>
+        <v>0.0002092472714139149</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0001255277311429381</v>
+        <v>0.0003079622401855886</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0001022763171931729</v>
+        <v>0.001203796360641718</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.00011681136675179</v>
+        <v>7.869857654441148e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>3.702720277942717e-05</v>
+        <v>0.0008917192462831736</v>
       </c>
       <c r="GA3" t="n">
-        <v>5.067266101832502e-05</v>
+        <v>0.0005396463093347847</v>
       </c>
       <c r="GB3" t="n">
-        <v>9.565801883582026e-05</v>
+        <v>0.0007377401343546808</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.0001927304256241769</v>
+        <v>0.001237788936123252</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.0001080791844287887</v>
+        <v>0.0004074039752595127</v>
       </c>
       <c r="GE3" t="n">
-        <v>8.948209870141e-05</v>
+        <v>0.001585265621542931</v>
       </c>
       <c r="GF3" t="n">
-        <v>8.112670911941677e-05</v>
+        <v>0.0001010463747661561</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.000223732422455214</v>
+        <v>0.0001458096376154572</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0001752328826114535</v>
+        <v>0.002119359560310841</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002700346987694502</v>
+        <v>0.03183358907699585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002093990915454924</v>
+        <v>0.006350377574563026</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002817261964082718</v>
+        <v>0.0136984046548605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005509101320058107</v>
+        <v>0.001625974895432591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009713729959912598</v>
+        <v>0.009980561211705208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001880146010080352</v>
+        <v>0.0009875684045255184</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0005602858145721257</v>
+        <v>0.002437467919662595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009820587001740932</v>
+        <v>0.003144776448607445</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006180297932587564</v>
+        <v>0.00304764648899436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002220896538347006</v>
+        <v>0.02772606909275055</v>
       </c>
       <c r="L4" t="n">
-        <v>7.415593427140266e-05</v>
+        <v>0.01031963527202606</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002050068229436874</v>
+        <v>0.01841474883258343</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004180139221716672</v>
+        <v>0.005459978245198727</v>
       </c>
       <c r="O4" t="n">
-        <v>3.790108166867867e-06</v>
+        <v>0.0006090376991778612</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007346653146669269</v>
+        <v>0.004674799740314484</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000410724722314626</v>
+        <v>0.001855712616816163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005866450374014676</v>
+        <v>0.0016902144998312</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0006842287839390337</v>
+        <v>0.004863503389060497</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007466358365491033</v>
+        <v>0.004045993555337191</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001288682396989316</v>
+        <v>0.002959613222628832</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001427005918230861</v>
+        <v>0.005391791462898254</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003861178993247449</v>
+        <v>0.0002478155656717718</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001629582839086652</v>
+        <v>0.003286885563284159</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001186093140859157</v>
+        <v>0.005204126704484224</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001883594813989475</v>
+        <v>0.002987990621477365</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001809086243156344</v>
+        <v>0.007155333179980516</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0001577161310706288</v>
+        <v>0.0004613134078681469</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0009622791549190879</v>
+        <v>0.003825822845101357</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0007675854722037911</v>
+        <v>0.0002458064700476825</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0003521849284879863</v>
+        <v>0.008498294278979301</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0004480430216062814</v>
+        <v>0.006829037331044674</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0002992809168063104</v>
+        <v>0.0007433153223246336</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0001365115167573094</v>
+        <v>0.00250034686177969</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0003368219186086208</v>
+        <v>0.002483174204826355</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.145997369661927e-05</v>
+        <v>0.005552538670599461</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0002166427002521232</v>
+        <v>0.007839342579245567</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0004901908105239272</v>
+        <v>0.01068862713873386</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0001606652367627248</v>
+        <v>0.003221339546144009</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0002757058828137815</v>
+        <v>0.00263658189214766</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0002217137807747349</v>
+        <v>0.0131195355206728</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0004969037836417556</v>
+        <v>0.003067885525524616</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.292800101917237e-05</v>
+        <v>0.003197504673153162</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0005807119305245578</v>
+        <v>0.001756357494741678</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0001139475789386779</v>
+        <v>0.003706971183419228</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0002804333926178515</v>
+        <v>0.007461086381226778</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0007657895912416279</v>
+        <v>0.01365367509424686</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0004595481732394546</v>
+        <v>0.001580038806423545</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001951125101186335</v>
+        <v>0.00464068166911602</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001370861427858472</v>
+        <v>0.0003612230939324945</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001878253533504903</v>
+        <v>0.004477140493690968</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0005307373940013349</v>
+        <v>0.0001878912444226444</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0001941142836585641</v>
+        <v>0.002948370296508074</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0006598488544113934</v>
+        <v>0.005577064119279385</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.591570228105411e-05</v>
+        <v>0.003061219118535519</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001091955229640007</v>
+        <v>0.009938519448041916</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0001962548412848264</v>
+        <v>0.003835451789200306</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0008072644704952836</v>
+        <v>0.0003406280884519219</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0002451814361847937</v>
+        <v>0.002673645736649632</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0008850552840158343</v>
+        <v>0.00392574816942215</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0001562181278131902</v>
+        <v>0.001564919017255306</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0003863192687276751</v>
+        <v>0.0005386351840570569</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.966337630525231e-05</v>
+        <v>0.001335586421191692</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004650161718018353</v>
+        <v>0.005778581369668245</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.124298619804904e-05</v>
+        <v>0.009784296154975891</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0001121466921176761</v>
+        <v>0.0006326937000267208</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0006404254236258566</v>
+        <v>0.002161313779652119</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.070651190588251e-05</v>
+        <v>0.00219182763248682</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001085997282643802</v>
+        <v>0.002421371173113585</v>
       </c>
       <c r="BR4" t="n">
-        <v>5.094037624076009e-05</v>
+        <v>0.002743812743574381</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0004117742064408958</v>
+        <v>0.004313483834266663</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.613530786125921e-06</v>
+        <v>0.003219400299713016</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0005459795356728137</v>
+        <v>0.006314429454505444</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0004904954112134874</v>
+        <v>0.01124805212020874</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0003417376428842545</v>
+        <v>7.627496961504221e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0006602754583582282</v>
+        <v>0.001998970750719309</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0005434253835119307</v>
+        <v>0.002147585619240999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0003164806985296309</v>
+        <v>0.006376826670020819</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.595866529503837e-05</v>
+        <v>0.0001782113686203957</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.752457607537508e-05</v>
+        <v>0.002022534841671586</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0003589528205338866</v>
+        <v>0.006481001619249582</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.980344131879974e-05</v>
+        <v>0.006592710502445698</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0004239256086293608</v>
+        <v>0.008933235891163349</v>
       </c>
       <c r="CF4" t="n">
-        <v>7.171875768108293e-05</v>
+        <v>0.003486837958917022</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0005138127598911524</v>
+        <v>0.004506880417466164</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0002843779511749744</v>
+        <v>0.001097293104976416</v>
       </c>
       <c r="CI4" t="n">
-        <v>9.286287422582973e-06</v>
+        <v>0.0009726010612212121</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.510215901769698e-05</v>
+        <v>0.001340344198979437</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0001195943768834695</v>
+        <v>0.00066879962105304</v>
       </c>
       <c r="CL4" t="n">
-        <v>7.326584454858676e-05</v>
+        <v>0.0003404991002753377</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0003011866356246173</v>
+        <v>0.002733806148171425</v>
       </c>
       <c r="CN4" t="n">
-        <v>7.411980186589062e-05</v>
+        <v>0.006173401139676571</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0001972016616491601</v>
+        <v>0.006185039877891541</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0005613559042103589</v>
+        <v>0.000662586186081171</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0003069659578613937</v>
+        <v>0.0003747623122762889</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0005085476441308856</v>
+        <v>0.004577906802296638</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0007435629377141595</v>
+        <v>0.001294005429372191</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.788510417100042e-06</v>
+        <v>0.006052916869521141</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002820738882292062</v>
+        <v>0.004932994022965431</v>
       </c>
       <c r="CV4" t="n">
-        <v>9.734612103784457e-05</v>
+        <v>0.005869964137673378</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0005473069031722844</v>
+        <v>0.008101005107164383</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0001619127579033375</v>
+        <v>0.004281377885490656</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0005333187873475254</v>
+        <v>0.004113423638045788</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001752047828631476</v>
+        <v>0.001262374455109239</v>
       </c>
       <c r="DA4" t="n">
-        <v>9.961212344933301e-05</v>
+        <v>0.002232050290331244</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.149012289009988e-05</v>
+        <v>0.001128529896959662</v>
       </c>
       <c r="DC4" t="n">
-        <v>4.799437374458648e-05</v>
+        <v>0.0001180738763650879</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.14270577696152e-05</v>
+        <v>0.001193574047647417</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.000661655270960182</v>
+        <v>0.000880188774317503</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00195259740576148</v>
+        <v>0.006891957018524408</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.391478821868077e-05</v>
+        <v>0.008043675683438778</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0007214350625872612</v>
+        <v>0.001820069155655801</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0003691542369779199</v>
+        <v>0.0008023903355933726</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002874850179068744</v>
+        <v>0.007272365037351847</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0006215076427906752</v>
+        <v>0.003226832719519734</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002515112864784896</v>
+        <v>0.004127880558371544</v>
       </c>
       <c r="DM4" t="n">
-        <v>8.757317846175283e-05</v>
+        <v>0.002406536135822535</v>
       </c>
       <c r="DN4" t="n">
-        <v>8.00712441559881e-05</v>
+        <v>0.0009246984263882041</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0005899394163861871</v>
+        <v>0.0042470907792449</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.321956319268793e-05</v>
+        <v>0.005405814852565527</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.000198089488549158</v>
+        <v>0.005490139126777649</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0007511673029512167</v>
+        <v>0.001679376699030399</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001453224394936115</v>
+        <v>0.002096430864185095</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0002844587143044919</v>
+        <v>0.002556803869083524</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0001375462888972834</v>
+        <v>0.0007097270572558045</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0003046354104299098</v>
+        <v>0.006079535931348801</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.000279464409686625</v>
+        <v>0.002406680723652244</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0004437377792783082</v>
+        <v>0.003247450338676572</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0002078078832710162</v>
+        <v>0.001762011903338134</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0005191359086893499</v>
+        <v>0.000510679732542485</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.000238471373450011</v>
+        <v>0.001798348617739975</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.000302634114632383</v>
+        <v>0.0002401568926870823</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0001058126144926064</v>
+        <v>0.0005710539408028126</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.000160362891620025</v>
+        <v>0.0005871857865713537</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001537147763883695</v>
+        <v>0.005228589288890362</v>
       </c>
       <c r="EF4" t="n">
-        <v>9.548032539896667e-05</v>
+        <v>0.009011874906718731</v>
       </c>
       <c r="EG4" t="n">
-        <v>6.715211929986253e-05</v>
+        <v>0.008847313933074474</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002655309799592942</v>
+        <v>0.002111114095896482</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0001903979136841372</v>
+        <v>0.003299758303910494</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0002884980931412429</v>
+        <v>0.003014718880876899</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0001738803111948073</v>
+        <v>0.000218848988879472</v>
       </c>
       <c r="EL4" t="n">
-        <v>8.545025775674731e-05</v>
+        <v>0.0008163322927430272</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002774797030724585</v>
+        <v>0.001315329456701875</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0003608725382946432</v>
+        <v>0.00122175004798919</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002033435885095969</v>
+        <v>0.005999904591590166</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003586459788493812</v>
+        <v>0.001685403054580092</v>
       </c>
       <c r="EQ4" t="n">
-        <v>6.885704351589084e-06</v>
+        <v>0.0002710734552238137</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0003062231699004769</v>
+        <v>0.002346755005419254</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001791140239220113</v>
+        <v>0.001903386320918798</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0002385124244028702</v>
+        <v>0.003550013760104775</v>
       </c>
       <c r="EU4" t="n">
-        <v>7.542346429545432e-05</v>
+        <v>0.0007685100426897407</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002040623221546412</v>
+        <v>0.006262114737182856</v>
       </c>
       <c r="EW4" t="n">
-        <v>9.428501653019339e-05</v>
+        <v>0.00140415329951793</v>
       </c>
       <c r="EX4" t="n">
-        <v>8.353660814464092e-05</v>
+        <v>0.006555438041687012</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0005018844385631382</v>
+        <v>0.007897478528320789</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.297834362252615e-05</v>
+        <v>0.003641089890152216</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0004481895011849701</v>
+        <v>0.003752692369744182</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0001118719956139103</v>
+        <v>0.0001742348540574312</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0001886640238808468</v>
+        <v>0.001458383048884571</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.138263153028674e-05</v>
+        <v>0.0004628659808076918</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.101479185512289e-05</v>
+        <v>8.06746247690171e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>4.008887481177226e-05</v>
+        <v>0.001467123394832015</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0004359505837783217</v>
+        <v>0.004599352367222309</v>
       </c>
       <c r="FH4" t="n">
-        <v>7.977783388923854e-05</v>
+        <v>0.002513548592105508</v>
       </c>
       <c r="FI4" t="n">
-        <v>2.005361602641642e-05</v>
+        <v>0.005219772458076477</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0002305397792952135</v>
+        <v>0.000480052171042189</v>
       </c>
       <c r="FK4" t="n">
-        <v>7.62247436796315e-05</v>
+        <v>0.002108005806803703</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0001176091318484396</v>
+        <v>0.0002723055658861995</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0004780861199833453</v>
+        <v>0.0007426093798130751</v>
       </c>
       <c r="FN4" t="n">
-        <v>9.39233141252771e-05</v>
+        <v>0.007344691082835197</v>
       </c>
       <c r="FO4" t="n">
-        <v>9.669250721344724e-05</v>
+        <v>0.003995194565504789</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.994013215764426e-05</v>
+        <v>0.008856723085045815</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0003120303153991699</v>
+        <v>0.008505675941705704</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.000546887400560081</v>
+        <v>0.001709138043224812</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0005385011900216341</v>
+        <v>0.009576721116900444</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0007006886298768222</v>
+        <v>0.008098594844341278</v>
       </c>
       <c r="FU4" t="n">
-        <v>6.131544796517119e-05</v>
+        <v>0.001546805957332253</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0002276521699968725</v>
+        <v>0.008481827564537525</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0003550576802808791</v>
+        <v>0.006577488966286182</v>
       </c>
       <c r="FX4" t="n">
-        <v>5.579309072345495e-05</v>
+        <v>0.0007892494322732091</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.000221220325329341</v>
+        <v>0.004802458919584751</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0004417061281856149</v>
+        <v>0.008179377764463425</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001160807150881737</v>
+        <v>0.002887681126594543</v>
       </c>
       <c r="GB4" t="n">
-        <v>3.562652636901475e-05</v>
+        <v>0.003379961242899299</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.001339349080808461</v>
+        <v>0.003686055773869157</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0007903848309069872</v>
+        <v>0.003308440092951059</v>
       </c>
       <c r="GE4" t="n">
-        <v>9.287604916607961e-05</v>
+        <v>0.009759190492331982</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0006017175037413836</v>
+        <v>0.003687337506562471</v>
       </c>
       <c r="GG4" t="n">
-        <v>6.379190017469227e-05</v>
+        <v>0.0005019255913794041</v>
       </c>
     </row>
     <row r="5">
@@ -3275,571 +3275,571 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.01161121018230915</v>
+        <v>0.0006285635754466057</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04996137693524361</v>
+        <v>0.009763564914464951</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004602121654897928</v>
+        <v>0.001041475217789412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01871274597942829</v>
+        <v>0.008765035308897495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007353690452873707</v>
+        <v>0.001454907585866749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01279010158032179</v>
+        <v>0.001992260804399848</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000998207600787282</v>
+        <v>0.003694254904985428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002090171212330461</v>
+        <v>0.003072499763220549</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002396916737779975</v>
+        <v>3.708603617269546e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0150246936827898</v>
+        <v>3.568458487279713e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03098365664482117</v>
+        <v>0.01005617622286081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006380101549439132</v>
+        <v>0.002178932307288051</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01892995461821556</v>
+        <v>0.01205522753298283</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01283747982233763</v>
+        <v>0.002731280634179711</v>
       </c>
       <c r="O6" t="n">
-        <v>0.019154267385602</v>
+        <v>0.001051582046784461</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002260340843349695</v>
+        <v>0.004264605697244406</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001538039650768042</v>
+        <v>0.000114638009108603</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004503856413066387</v>
+        <v>6.806815508753061e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008185164770111442</v>
+        <v>8.295442967209965e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004650778137147427</v>
+        <v>0.0004916262114420533</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003158505307510495</v>
+        <v>0.0006458807620219886</v>
       </c>
       <c r="V6" t="n">
-        <v>0.006978957913815975</v>
+        <v>4.951797745889053e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005503055173903704</v>
+        <v>0.0009498157305642962</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003413858823478222</v>
+        <v>0.001507859211415052</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005524854175746441</v>
+        <v>0.001359410583972931</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002823147224262357</v>
+        <v>0.002042983658611774</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.004707794636487961</v>
+        <v>0.001983743859454989</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00155320018529892</v>
+        <v>5.916011286899447e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.009246706962585449</v>
+        <v>3.93787631765008e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.001582579337991774</v>
+        <v>0.0007802796899341047</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001115871244110167</v>
+        <v>0.002171289641410112</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.004690067376941442</v>
+        <v>0.0008293297723866999</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0001673018559813499</v>
+        <v>0.002112692920491099</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001157126040197909</v>
+        <v>0.0009347659070044756</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0009389698971062899</v>
+        <v>0.0002968054614029825</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001711264485493302</v>
+        <v>0.0004201562260277569</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.004308987408876419</v>
+        <v>0.0003036285343114287</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005047379992902279</v>
+        <v>0.002347792498767376</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001003169803880155</v>
+        <v>0.001301350770518184</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.002248701639473438</v>
+        <v>0.002317097038030624</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.004084438551217318</v>
+        <v>0.001097977161407471</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.005848766304552555</v>
+        <v>0.001964129041880369</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.000192031788174063</v>
+        <v>0.0006417840486392379</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0005876008654013276</v>
+        <v>0.0005480003310367465</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.003304399782791734</v>
+        <v>0.0002441970573272556</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0004964619292877614</v>
+        <v>0.0003731396573130041</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03341881558299065</v>
+        <v>0.004888824187219143</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.000884064647834748</v>
+        <v>0.00018237745098304</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.003423321060836315</v>
+        <v>0.00436547864228487</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.003440529108047485</v>
+        <v>0.00653592636808753</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.001506834872998297</v>
+        <v>0.001410239026881754</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001309146406129003</v>
+        <v>0.0004891890566796064</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.00140665820799768</v>
+        <v>0.0009069572552107275</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.005804335698485374</v>
+        <v>0.001012794673442841</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.005144141614437103</v>
+        <v>0.0005583542515523732</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.008338067680597305</v>
+        <v>0.0009716071654111147</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.007273061666637659</v>
+        <v>0.001430210424587131</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.002167194848880172</v>
+        <v>0.0008100525592453778</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01273408066481352</v>
+        <v>0.002833049511536956</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.007250393275171518</v>
+        <v>0.0009819709230214357</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.003158980282023549</v>
+        <v>0.0009013492381200194</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.004153651650995016</v>
+        <v>0.002918644342571497</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0006503391778096557</v>
+        <v>0.001186980749480426</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.003567385254427791</v>
+        <v>0.000463743694126606</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.004722492303699255</v>
+        <v>0.0003960423055104911</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.00164468155708164</v>
+        <v>0.0003018070128746331</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.006718330550938845</v>
+        <v>0.001437762985005975</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.003650496248155832</v>
+        <v>0.0007657702080905437</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.003484690329059958</v>
+        <v>0.0006066385540179908</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.003721647197380662</v>
+        <v>2.265638613607734e-05</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0003872410743497312</v>
+        <v>0.0005306924576871097</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.003647868055850267</v>
+        <v>0.0001268855994567275</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001211814087582752</v>
+        <v>9.548407979309559e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01547759585082531</v>
+        <v>0.003125245217233896</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.003116034436970949</v>
+        <v>0.0006823945441283286</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.004515847656875849</v>
+        <v>0.003426739946007729</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.003944436088204384</v>
+        <v>0.001100861001759768</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.007623751647770405</v>
+        <v>0.001761596649885178</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.001596835092641413</v>
+        <v>0.001783116022124887</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0007627077866345644</v>
+        <v>0.0003824309387709945</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.004295964259654284</v>
+        <v>0.00118859380017966</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.003018047427758574</v>
+        <v>6.041384767740965e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.00835881382226944</v>
+        <v>0.00318507244810462</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.003167048562318087</v>
+        <v>0.0005150407087057829</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.001117721549235284</v>
+        <v>0.003261183388531208</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001834821072407067</v>
+        <v>0.0004331979143898934</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.003788364119827747</v>
+        <v>9.389677870785818e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.001326210796833038</v>
+        <v>5.406578566180542e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0004226708551868796</v>
+        <v>0.0001172305637737736</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.001594136352650821</v>
+        <v>0.0002694469003472477</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.003347980324178934</v>
+        <v>0.0006925425259396434</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0001658957917243242</v>
+        <v>0.003057294525206089</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.004790054634213448</v>
+        <v>0.002938587218523026</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.006646744441241026</v>
+        <v>0.004095807205885649</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004083591513335705</v>
+        <v>0.0004279248823877424</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.004664166830480099</v>
+        <v>0.001168924616649747</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.003388748271390796</v>
+        <v>0.0007889387779869139</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.004130909219384193</v>
+        <v>0.001142294029705226</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.001517609460279346</v>
+        <v>0.0008510940242558718</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.002475100103765726</v>
+        <v>8.59463689266704e-05</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.006569864228367805</v>
+        <v>0.003206536639481783</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.002992428373545408</v>
+        <v>0.0006448145722970366</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.003544334089383483</v>
+        <v>0.003500388003885746</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001957102678716183</v>
+        <v>0.0008465173887088895</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.004496348556131124</v>
+        <v>9.824566222960129e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001695811515673995</v>
+        <v>0.0001212958595715463</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0006260422524064779</v>
+        <v>0.0001712245866656303</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.001053637126460671</v>
+        <v>0.00054492789786309</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.005704057868570089</v>
+        <v>0.001138930441811681</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.00283476896584034</v>
+        <v>0.001768101705238223</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.002074589719995856</v>
+        <v>3.84728773497045e-05</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.008092693984508514</v>
+        <v>0.002759895753115416</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.006417172029614449</v>
+        <v>0.0004874195146840066</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0006837413529865444</v>
+        <v>0.003188961884006858</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.002522854600101709</v>
+        <v>0.0006642239750362933</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.000823465408757329</v>
+        <v>0.003798827761784196</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0007959709037095308</v>
+        <v>0.001448306022211909</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.005083735100924969</v>
+        <v>0.0001358029549010098</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.001819520373828709</v>
+        <v>0.001651782891713083</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.004291539080440998</v>
+        <v>0.0005395550397224724</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0003304334240965545</v>
+        <v>0.001997231971472502</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001092620310373604</v>
+        <v>0.0001289026404265314</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00675984937697649</v>
+        <v>0.0006547056254930794</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.000661770231090486</v>
+        <v>0.002432295819744468</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.001220718142576516</v>
+        <v>0.0007106935372576118</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.002390509704127908</v>
+        <v>0.00384886097162962</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.002683232538402081</v>
+        <v>6.806102464906871e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0001572366163600236</v>
+        <v>0.0006907236529514194</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.008515625260770321</v>
+        <v>0.0009687147103250027</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.002581855282187462</v>
+        <v>0.001725529204122722</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.005511761177331209</v>
+        <v>0.00110146077349782</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0006500793970189989</v>
+        <v>0.002113450318574905</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0004838371824007481</v>
+        <v>9.246485569747165e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0009843312436714768</v>
+        <v>0.005141966976225376</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.003146046306937933</v>
+        <v>0.003263395978137851</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0001012731809169054</v>
+        <v>0.001153028337284923</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.004250977654010057</v>
+        <v>0.002128529595211148</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001340199378319085</v>
+        <v>0.0009157692547887564</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0001684500020928681</v>
+        <v>0.002906028646975756</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0002392923342995346</v>
+        <v>0.0008863412658683956</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.002289786003530025</v>
+        <v>0.0001386856893077493</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.002501562004908919</v>
+        <v>0.0003646960249170661</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0009444323368370533</v>
+        <v>8.169756620191038e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>7.755344267934561e-05</v>
+        <v>0.0003252141759730875</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.003265243489295244</v>
+        <v>0.0009140745969489217</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.007154325488954782</v>
+        <v>0.003017062786966562</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.001753302058205009</v>
+        <v>1.677218824625015e-05</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.004199613817036152</v>
+        <v>0.00181952805723995</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.005253963638097048</v>
+        <v>0.0008848991710692644</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01271477807313204</v>
+        <v>0.0005070981569588184</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.003347849473357201</v>
+        <v>0.001528953784145415</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.006112020928412676</v>
+        <v>0.000550961762201041</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001202260260470212</v>
+        <v>0.002129684668034315</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.001892006723210216</v>
+        <v>0.0001041790965246037</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.006931561511009932</v>
+        <v>0.003406916512176394</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0007583671831525862</v>
+        <v>0.0004305322363507003</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.002376982709392905</v>
+        <v>0.003707371419295669</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001539261313155293</v>
+        <v>0.0005138196283951402</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.004798147827386856</v>
+        <v>0.0002507076424080878</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.002077148761600256</v>
+        <v>0.0003460553416516632</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0006405276944860816</v>
+        <v>0.000504696334246546</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.002029714873060584</v>
+        <v>0.0006545283831655979</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.001429219148121774</v>
+        <v>0.0002604128676466644</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.002947454806417227</v>
+        <v>0.001008592080324888</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.002280612476170063</v>
+        <v>0.0008991624345071614</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.004997802432626486</v>
+        <v>0.001529418863356113</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.001571888453327119</v>
+        <v>0.001376463449560106</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.001765840221196413</v>
+        <v>0.001421243185177445</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.001612978288903832</v>
+        <v>0.0009792170021682978</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.004069521557539701</v>
+        <v>0.002477838192135096</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.006616830825805664</v>
+        <v>0.000611851632129401</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.003251183778047562</v>
+        <v>0.002394587267190218</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.005236636381596327</v>
+        <v>0.003442565444856882</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.003012689528986812</v>
+        <v>0.0004073382588103414</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.004063725005835295</v>
+        <v>0.002405006438493729</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01417955942451954</v>
+        <v>0.002869096118956804</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004688437562435865</v>
+        <v>0.002439933829009533</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0006662225350737572</v>
+        <v>0.001110548386350274</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.002518803346902132</v>
+        <v>0.0005622087046504021</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.00278389360755682</v>
+        <v>0.003299332223832607</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.005505022592842579</v>
+        <v>0.001050188555382192</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.003372046397998929</v>
+        <v>0.00110357953235507</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.003677301341667771</v>
+        <v>0.0005707896780222654</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.001925599295645952</v>
+        <v>0.003130110213533044</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.004976941738277674</v>
+        <v>0.002626216504722834</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.002801233669742942</v>
+        <v>0.0005537333781830966</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.01060112379491329</v>
+        <v>0.003432929515838623</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0001824531937018037</v>
+        <v>0.0003757125814445317</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001842366298660636</v>
+        <v>0.0005013826303184032</v>
       </c>
     </row>
     <row r="7">
@@ -4413,1140 +4413,1140 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0004258544649928808</v>
+        <v>0.0004817182198166847</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00151656090747565</v>
+        <v>0.1005513519048691</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001469698618166149</v>
+        <v>0.02185845747590065</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006376969395205379</v>
+        <v>0.01805021800100803</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004557188658509403</v>
+        <v>0.001184698194265366</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0005719829350709915</v>
+        <v>0.06160654127597809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002866685972549021</v>
+        <v>0.04040407761931419</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001106249910662882</v>
+        <v>0.04370678588747978</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001928987476276234</v>
+        <v>0.02858213894069195</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003787971800193191</v>
+        <v>0.02380309998989105</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001006391132250428</v>
+        <v>0.1004419177770615</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001472193980589509</v>
+        <v>0.01614973694086075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0008499374380335212</v>
+        <v>0.04855289310216904</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0006197098991833627</v>
+        <v>0.03736103698611259</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0007283980958163738</v>
+        <v>0.06523333489894867</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0004115935298614204</v>
+        <v>0.01859350502490997</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0004190234176348895</v>
+        <v>0.01400084234774113</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001059106798493303</v>
+        <v>0.05500752478837967</v>
       </c>
       <c r="S8" t="n">
-        <v>4.704211460193619e-05</v>
+        <v>0.008485384285449982</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003005140752065927</v>
+        <v>0.05117093771696091</v>
       </c>
       <c r="U8" t="n">
-        <v>5.751228673034348e-05</v>
+        <v>0.00572561752051115</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001272555236937478</v>
+        <v>0.02428699657320976</v>
       </c>
       <c r="W8" t="n">
-        <v>6.859382119728252e-05</v>
+        <v>0.01994960941374302</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002080661506624892</v>
+        <v>0.01836999133229256</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001052348525263369</v>
+        <v>0.00437976373359561</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.311526597826742e-06</v>
+        <v>0.005936904344707727</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.96525671123527e-05</v>
+        <v>0.01202825177460909</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.723439582856372e-05</v>
+        <v>0.004448531195521355</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0002924934378825128</v>
+        <v>0.001379851251840591</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0002005381393246353</v>
+        <v>0.02205696329474449</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0004280424909666181</v>
+        <v>0.04630061611533165</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0001915619650389999</v>
+        <v>0.03672706335783005</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.054531250905711e-05</v>
+        <v>0.02413923293352127</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002120804565493017</v>
+        <v>0.008138220757246017</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.299523086752743e-06</v>
+        <v>0.06565608084201813</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001155326317530125</v>
+        <v>0.008266538381576538</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0002290838165208697</v>
+        <v>0.002276026643812656</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0002561921428423375</v>
+        <v>0.03892562538385391</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.836754199757706e-05</v>
+        <v>0.005255751311779022</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.206641511293128e-06</v>
+        <v>0.01995178684592247</v>
       </c>
       <c r="AO8" t="n">
-        <v>6.720482633681968e-05</v>
+        <v>0.01955381408333778</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001761274470482022</v>
+        <v>0.02276812121272087</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001594347559148446</v>
+        <v>0.001640591770410538</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0001027247999445535</v>
+        <v>0.05853311717510223</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.844497304176912e-05</v>
+        <v>0.008670521900057793</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0001905081735458225</v>
+        <v>0.00478079728782177</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001267263200134039</v>
+        <v>0.128642737865448</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.630728603340685e-05</v>
+        <v>0.002737214788794518</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.959135837154463e-05</v>
+        <v>0.001569054205901921</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001747385831549764</v>
+        <v>0.005546706262975931</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0001660908164922148</v>
+        <v>0.05527469143271446</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0003184124652761966</v>
+        <v>0.006406967528164387</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.548546035541221e-05</v>
+        <v>0.02837250009179115</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.193583663436584e-05</v>
+        <v>0.01944926008582115</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0001834799768403172</v>
+        <v>0.002321802079677582</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002309472329216078</v>
+        <v>0.03959730267524719</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0002095178788295016</v>
+        <v>0.0291092824190855</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.072414155118167e-05</v>
+        <v>0.02926484495401382</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.000608104863204062</v>
+        <v>0.06039279326796532</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.000253130798228085</v>
+        <v>0.01921681500971317</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001190305920317769</v>
+        <v>0.02051136083900928</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0003154552832711488</v>
+        <v>0.007328792009502649</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0002028158487519249</v>
+        <v>0.0277105700224638</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001351422106381506</v>
+        <v>0.01014134287834167</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0002576452388893813</v>
+        <v>0.01130834687501192</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.344454595819116e-05</v>
+        <v>0.01160098426043987</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.000305521214613691</v>
+        <v>0.02538859099149704</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002780763024929911</v>
+        <v>0.01237006857991219</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.254423740552738e-07</v>
+        <v>0.01899725943803787</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0002243283379357308</v>
+        <v>0.03037075325846672</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.394033279211726e-05</v>
+        <v>0.01001172326505184</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.531327380798757e-05</v>
+        <v>0.02044293284416199</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.51282277633436e-05</v>
+        <v>0.01626226492226124</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.000516423606313765</v>
+        <v>0.121185764670372</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.01035382412374e-05</v>
+        <v>0.01461654808372259</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001610086765140295</v>
+        <v>0.02204874530434608</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.950541814556345e-05</v>
+        <v>0.0267414003610611</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000245898001594469</v>
+        <v>0.006419846322387457</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.626738468185067e-05</v>
+        <v>0.02518871240317822</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0001050140708684921</v>
+        <v>0.001924325712025166</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.642669955501333e-05</v>
+        <v>0.0008324314840137959</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.769378185505047e-05</v>
+        <v>0.006748745683580637</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003122377092950046</v>
+        <v>0.03948521614074707</v>
       </c>
       <c r="CF8" t="n">
-        <v>6.858172855572775e-05</v>
+        <v>0.006048922426998615</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0001239362318301573</v>
+        <v>0.006043559871613979</v>
       </c>
       <c r="CH8" t="n">
-        <v>4.219688707962632e-05</v>
+        <v>0.006479346659034491</v>
       </c>
       <c r="CI8" t="n">
-        <v>9.659393253969029e-05</v>
+        <v>0.01133318245410919</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0001139724627137184</v>
+        <v>0.004338999278843403</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.847951716626994e-05</v>
+        <v>0.005383652169257402</v>
       </c>
       <c r="CL8" t="n">
-        <v>5.186738417251036e-05</v>
+        <v>0.002392116235569119</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0002669363166205585</v>
+        <v>0.01749686151742935</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002167769416701049</v>
+        <v>0.06915637850761414</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0001781019527697936</v>
+        <v>0.003583315759897232</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0001922932715388015</v>
+        <v>0.02584359608590603</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001911844010464847</v>
+        <v>0.03842728585004807</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0003080300521105528</v>
+        <v>0.00372530659660697</v>
       </c>
       <c r="CS8" t="n">
-        <v>1.254920243809465e-05</v>
+        <v>0.02766036614775658</v>
       </c>
       <c r="CT8" t="n">
-        <v>9.080316522158682e-05</v>
+        <v>0.02661767229437828</v>
       </c>
       <c r="CU8" t="n">
-        <v>3.731203469214961e-05</v>
+        <v>0.005869511980563402</v>
       </c>
       <c r="CV8" t="n">
-        <v>4.502571755438112e-05</v>
+        <v>0.001425393391400576</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0002343773230677471</v>
+        <v>0.03632266074419022</v>
       </c>
       <c r="CX8" t="n">
-        <v>6.40864236629568e-05</v>
+        <v>0.006319453008472919</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001964702532859519</v>
+        <v>0.003980007953941822</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.221866270701867e-05</v>
+        <v>0.007237355224788189</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001321892341366038</v>
+        <v>0.01257530692964792</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001319208386121318</v>
+        <v>0.004515670239925385</v>
       </c>
       <c r="DC8" t="n">
-        <v>5.237707955529913e-05</v>
+        <v>0.003507206914946437</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.282211037003435e-05</v>
+        <v>0.0007195370271801949</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0001035835957736708</v>
+        <v>0.02076718956232071</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0004458418115973473</v>
+        <v>0.06970030069351196</v>
       </c>
       <c r="DG8" t="n">
-        <v>9.180314373224974e-05</v>
+        <v>0.02809569239616394</v>
       </c>
       <c r="DH8" t="n">
-        <v>6.596879393327981e-05</v>
+        <v>0.02057241275906563</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0004752922977786511</v>
+        <v>0.02475592121481895</v>
       </c>
       <c r="DJ8" t="n">
-        <v>4.055798490298912e-05</v>
+        <v>0.05570920556783676</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.000373650633264333</v>
+        <v>0.01958638615906239</v>
       </c>
       <c r="DL8" t="n">
-        <v>7.095831824699417e-05</v>
+        <v>0.04499876499176025</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0001649330952204764</v>
+        <v>0.03032942302525043</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0002371634473092854</v>
+        <v>0.004876465070992708</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0001952016173163429</v>
+        <v>0.01329283136874437</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0001233010989381</v>
+        <v>0.005876522976905107</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.000264049245743081</v>
+        <v>0.03562376275658607</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001038033733493648</v>
+        <v>0.01270513888448477</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0001515752519480884</v>
+        <v>0.006372491829097271</v>
       </c>
       <c r="DT8" t="n">
-        <v>7.03932746546343e-05</v>
+        <v>0.007524711545556784</v>
       </c>
       <c r="DU8" t="n">
-        <v>6.141026096884161e-05</v>
+        <v>0.006028271280229092</v>
       </c>
       <c r="DV8" t="n">
-        <v>9.138627501670271e-05</v>
+        <v>0.002277769381180406</v>
       </c>
       <c r="DW8" t="n">
-        <v>3.571778506739065e-05</v>
+        <v>0.009203583002090454</v>
       </c>
       <c r="DX8" t="n">
-        <v>8.501021511619911e-05</v>
+        <v>0.03102738223969936</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0002401776582701132</v>
+        <v>0.02148786000907421</v>
       </c>
       <c r="DZ8" t="n">
-        <v>7.162777183111757e-05</v>
+        <v>0.009204554371535778</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001696607650956139</v>
+        <v>0.01736969687044621</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0001003002325887792</v>
+        <v>0.008872766979038715</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.376547490712255e-05</v>
+        <v>0.00271649332717061</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001832199923228472</v>
+        <v>0.02926292270421982</v>
       </c>
       <c r="EE8" t="n">
-        <v>7.361453754128888e-05</v>
+        <v>0.02957972697913647</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0001288801722694188</v>
+        <v>0.003077917033806443</v>
       </c>
       <c r="EG8" t="n">
-        <v>1.379499735776335e-05</v>
+        <v>0.009395202621817589</v>
       </c>
       <c r="EH8" t="n">
-        <v>2.935959855676629e-05</v>
+        <v>0.004585145972669125</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001352900872007012</v>
+        <v>0.02374893799424171</v>
       </c>
       <c r="EJ8" t="n">
-        <v>3.561499033821747e-05</v>
+        <v>0.008350263349711895</v>
       </c>
       <c r="EK8" t="n">
-        <v>6.829289486631751e-05</v>
+        <v>0.01087968051433563</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0001666335010668263</v>
+        <v>0.006767173763364553</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.022420812863857e-05</v>
+        <v>0.01507880259305239</v>
       </c>
       <c r="EN8" t="n">
-        <v>3.118879249086604e-05</v>
+        <v>0.001288774888962507</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0002013749035540968</v>
+        <v>0.01359893474727869</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0001482191728428006</v>
+        <v>0.02555252611637115</v>
       </c>
       <c r="EQ8" t="n">
-        <v>3.272022149758413e-05</v>
+        <v>0.001560462173074484</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0001342292380286381</v>
+        <v>0.02452278137207031</v>
       </c>
       <c r="ES8" t="n">
-        <v>3.274669870734215e-05</v>
+        <v>0.05599022284150124</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0003629488637670875</v>
+        <v>0.006632721051573753</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0001873469154816121</v>
+        <v>0.01028191857039928</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.000241546455072239</v>
+        <v>0.02249863743782043</v>
       </c>
       <c r="EW8" t="n">
-        <v>2.881507862184662e-05</v>
+        <v>0.005403293296694756</v>
       </c>
       <c r="EX8" t="n">
-        <v>4.697895565186627e-05</v>
+        <v>0.005493533797562122</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.000220458023250103</v>
+        <v>0.04442713409662247</v>
       </c>
       <c r="EZ8" t="n">
-        <v>3.652840405266033e-06</v>
+        <v>0.00247450708411634</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0001444087538402528</v>
+        <v>0.0007921662181615829</v>
       </c>
       <c r="FB8" t="n">
-        <v>3.356487286509946e-05</v>
+        <v>0.008539487607777119</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0001493785239290446</v>
+        <v>0.01145496405661106</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0001323484029853716</v>
+        <v>0.002102692145854235</v>
       </c>
       <c r="FE8" t="n">
-        <v>1.982711182790808e-05</v>
+        <v>0.0009367275051772594</v>
       </c>
       <c r="FF8" t="n">
-        <v>5.883148696739227e-05</v>
+        <v>0.005841208156198263</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001701706642052159</v>
+        <v>0.01431652158498764</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0001916469191201031</v>
+        <v>0.02229248732328415</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.00010487693361938</v>
+        <v>0.003025725483894348</v>
       </c>
       <c r="FJ8" t="n">
-        <v>6.888022471684963e-05</v>
+        <v>0.0226932130753994</v>
       </c>
       <c r="FK8" t="n">
-        <v>4.534409163170494e-05</v>
+        <v>0.004209044389426708</v>
       </c>
       <c r="FL8" t="n">
-        <v>5.39328102604486e-05</v>
+        <v>0.03675882518291473</v>
       </c>
       <c r="FM8" t="n">
-        <v>3.693166217999533e-05</v>
+        <v>0.01447277516126633</v>
       </c>
       <c r="FN8" t="n">
-        <v>6.647210830124095e-05</v>
+        <v>0.03317495435476303</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0001187651796499267</v>
+        <v>0.02472073771059513</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.000198991212528199</v>
+        <v>0.01159980241209269</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0002333442389499396</v>
+        <v>0.01710995100438595</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0002566185430623591</v>
+        <v>0.01430325955152512</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00014134643424768</v>
+        <v>0.003226516768336296</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0005245179054327309</v>
+        <v>0.05656407028436661</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0003392415819689631</v>
+        <v>0.0409964956343174</v>
       </c>
       <c r="FV8" t="n">
-        <v>9.70703549683094e-05</v>
+        <v>0.02888575382530689</v>
       </c>
       <c r="FW8" t="n">
-        <v>8.893063204595819e-05</v>
+        <v>0.04363586381077766</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0001152378972619772</v>
+        <v>0.007049530744552612</v>
       </c>
       <c r="FY8" t="n">
-        <v>7.548858411610126e-05</v>
+        <v>0.01223007123917341</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0003204475506208837</v>
+        <v>0.02289900742471218</v>
       </c>
       <c r="GA8" t="n">
-        <v>1.288768817175878e-05</v>
+        <v>0.008761696517467499</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.000272472680080682</v>
+        <v>0.01346970908343792</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0001341932656941935</v>
+        <v>0.009742210619151592</v>
       </c>
       <c r="GD8" t="n">
-        <v>8.452955808024853e-05</v>
+        <v>0.02855342626571655</v>
       </c>
       <c r="GE8" t="n">
-        <v>9.152410348178819e-05</v>
+        <v>0.0008094478398561478</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0002005388669203967</v>
+        <v>0.0296257846057415</v>
       </c>
       <c r="GG8" t="n">
-        <v>8.723649443709292e-06</v>
+        <v>0.01955564320087433</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0002554201346356422</v>
+        <v>0.00204105768352747</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001933258608914912</v>
+        <v>0.0116162495687604</v>
       </c>
       <c r="C9" t="n">
-        <v>9.472017700318247e-05</v>
+        <v>0.002308258786797523</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0008546625613234937</v>
+        <v>0.009243689477443695</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004462434444576502</v>
+        <v>0.002019739942625165</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0004316592821851373</v>
+        <v>0.008218548260629177</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001555760245537385</v>
+        <v>0.004807425197213888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001668048207648098</v>
+        <v>0.004967388696968555</v>
       </c>
       <c r="I9" t="n">
-        <v>6.172934809001163e-05</v>
+        <v>0.0009624905651435256</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003665967960841954</v>
+        <v>0.001861782744526863</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001240702229551971</v>
+        <v>0.01151230931282043</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001234559022122994</v>
+        <v>0.004443113692104816</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009062357130460441</v>
+        <v>0.01307930052280426</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0008899269159883261</v>
+        <v>0.004515293054282665</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0007275561220012605</v>
+        <v>0.007240270264446735</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001148328301496804</v>
+        <v>0.005849611945450306</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001238649128936231</v>
+        <v>0.001818216638639569</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001079665962606668</v>
+        <v>0.001427071169018745</v>
       </c>
       <c r="S9" t="n">
-        <v>5.536824755836278e-05</v>
+        <v>0.001125652925111353</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0003484105400275439</v>
+        <v>7.227617606986314e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.673848550533876e-05</v>
+        <v>0.0007317699491977692</v>
       </c>
       <c r="V9" t="n">
-        <v>0.000249070959398523</v>
+        <v>1.082458857126767e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0001710022334009409</v>
+        <v>0.001427410170435905</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0002328236732864752</v>
+        <v>0.003393802093341947</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002098508266499266</v>
+        <v>0.0006169189582578838</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.887321018846706e-05</v>
+        <v>0.002076314529404044</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001246547035407275</v>
+        <v>0.002074020449072123</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001563710102345794</v>
+        <v>0.001830181339755654</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0002610859519336373</v>
+        <v>0.001910649007186294</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001054981112247333</v>
+        <v>0.002260910114273429</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.531270027044229e-05</v>
+        <v>0.0001194567885249853</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0001844408689066768</v>
+        <v>0.000970796390902251</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.66655575716868e-05</v>
+        <v>0.005177346989512444</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.405471215955913e-05</v>
+        <v>0.0001197362435050309</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.156562161166221e-05</v>
+        <v>0.002474571112543344</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.0548609578982e-05</v>
+        <v>0.001265686354599893</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001607240265002474</v>
+        <v>0.001162701286375523</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0002134655369445682</v>
+        <v>0.004047543741762638</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.852028268942377e-06</v>
+        <v>0.002729004481807351</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.27292785490863e-05</v>
+        <v>0.002058558864519</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0002365758409723639</v>
+        <v>0.000908179092220962</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0002734837180469185</v>
+        <v>0.002685496117919683</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.972565951291472e-05</v>
+        <v>0.00179764605127275</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.254242983530276e-05</v>
+        <v>0.0003956557775381953</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0001142104738391936</v>
+        <v>0.0008114882512018085</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0001834812865126878</v>
+        <v>0.0009679816430434585</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00143693364225328</v>
+        <v>0.006700403522700071</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.130286884494126e-05</v>
+        <v>0.002362489933148026</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0001496952609159052</v>
+        <v>0.004901519045233727</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0002281361521454528</v>
+        <v>0.008681423962116241</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.24698144645663e-05</v>
+        <v>0.006003769114613533</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001112827667384408</v>
+        <v>0.0001814802817534655</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.910821058321744e-05</v>
+        <v>2.085027517750859e-06</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.093175837420858e-05</v>
+        <v>0.00102163152769208</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.153717110166326e-05</v>
+        <v>0.001504517393186688</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0003163715300615877</v>
+        <v>0.0003592011053115129</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0002687149972189218</v>
+        <v>0.002292164601385593</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0001316421403316781</v>
+        <v>0.001432756311260164</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.000626243359874934</v>
+        <v>0.003553448477759957</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0003927407960873097</v>
+        <v>0.001068640034645796</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0002370804140809923</v>
+        <v>0.001437389524653554</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0001046237157424912</v>
+        <v>0.002757057081907988</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.011703979107551e-05</v>
+        <v>0.001779922633431852</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0002772693987935781</v>
+        <v>0.0007162683177739382</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0003319572715554386</v>
+        <v>0.0002286467351950705</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.816421253257431e-05</v>
+        <v>2.756057801889256e-05</v>
       </c>
       <c r="BO9" t="n">
-        <v>9.692746243672445e-05</v>
+        <v>0.001869490602985024</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0003025602491106838</v>
+        <v>0.0005227194633334875</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0002041509578702971</v>
+        <v>0.0004079099162481725</v>
       </c>
       <c r="BR9" t="n">
-        <v>8.813659951556474e-05</v>
+        <v>0.0002910142648033798</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.339740528143011e-05</v>
+        <v>0.001121834735386074</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0001643155119381845</v>
+        <v>0.0005455179489217699</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001445152593078092</v>
+        <v>0.0001981150708161294</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0007370630046352744</v>
+        <v>0.004466813057661057</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.714834646321833e-05</v>
+        <v>0.001508937566541135</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001373595005134121</v>
+        <v>0.005483022890985012</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.702563016209751e-05</v>
+        <v>0.002008427865803242</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0003447943308856338</v>
+        <v>0.004103985615074635</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.163844278082252e-05</v>
+        <v>0.001031149877235293</v>
       </c>
       <c r="CB9" t="n">
-        <v>9.957193105947226e-05</v>
+        <v>0.0004370892711449414</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0001258615520782769</v>
+        <v>0.001664764829911292</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001440707710571587</v>
+        <v>9.243344538845122e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0003191879077348858</v>
+        <v>0.003913639578968287</v>
       </c>
       <c r="CF9" t="n">
-        <v>9.738165681483224e-05</v>
+        <v>0.0003425536851864308</v>
       </c>
       <c r="CG9" t="n">
-        <v>7.638313400093466e-05</v>
+        <v>0.00359109346754849</v>
       </c>
       <c r="CH9" t="n">
-        <v>3.572559580788948e-05</v>
+        <v>5.625643098028377e-07</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001035796376527287</v>
+        <v>0.001575248665176332</v>
       </c>
       <c r="CJ9" t="n">
-        <v>4.882965004071593e-05</v>
+        <v>0.0003708484582602978</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.35939299070742e-05</v>
+        <v>0.0008217931026592851</v>
       </c>
       <c r="CL9" t="n">
-        <v>5.751432399847545e-05</v>
+        <v>1.490251452196389e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0002078368852380663</v>
+        <v>0.0007523640524595976</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0001835893344832584</v>
+        <v>0.001929443445987999</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.000107996427686885</v>
+        <v>0.004831405356526375</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0003509553789626807</v>
+        <v>0.005149243399500847</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0002998685231432319</v>
+        <v>0.0005217696889303625</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0002024346322286874</v>
+        <v>0.0012564726639539</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0001787391374818981</v>
+        <v>0.0008635994745418429</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0002925481821876019</v>
+        <v>0.001474929857067764</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.354087453364627e-05</v>
+        <v>0.00071129878051579</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0001242465950781479</v>
+        <v>1.401396002620459e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0002475104993209243</v>
+        <v>0.00372754642739892</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0001096094856620766</v>
+        <v>0.0008149056229740381</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001620938710402697</v>
+        <v>0.003918442875146866</v>
       </c>
       <c r="CZ9" t="n">
-        <v>3.963846756960265e-05</v>
+        <v>0.0009443438029848039</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001236835814779624</v>
+        <v>0.001781723811291158</v>
       </c>
       <c r="DB9" t="n">
-        <v>6.060966188670136e-05</v>
+        <v>0.0006008471827954054</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.975802999571897e-05</v>
+        <v>0.0006803305586799979</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.362189793027937e-05</v>
+        <v>0.0002894049976021051</v>
       </c>
       <c r="DE9" t="n">
-        <v>6.697494245599955e-05</v>
+        <v>0.0006297293584793806</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0003155352897010744</v>
+        <v>0.003561046905815601</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.533446215442382e-05</v>
+        <v>0.001052036066539586</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0003023584431502968</v>
+        <v>0.002954993862658739</v>
       </c>
       <c r="DI9" t="n">
-        <v>8.702307241037488e-05</v>
+        <v>0.0007528411806561053</v>
       </c>
       <c r="DJ9" t="n">
-        <v>5.648224760079756e-05</v>
+        <v>0.007496165111660957</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001172984266304411</v>
+        <v>0.001312713953666389</v>
       </c>
       <c r="DL9" t="n">
-        <v>3.699368244269863e-05</v>
+        <v>0.006493495311588049</v>
       </c>
       <c r="DM9" t="n">
-        <v>8.695494761923328e-05</v>
+        <v>0.002650935901328921</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0002046176668955013</v>
+        <v>0.0007313218084163964</v>
       </c>
       <c r="DO9" t="n">
-        <v>6.632119766436517e-05</v>
+        <v>0.001954244915395975</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001161317341029644</v>
+        <v>0.0003837755066342652</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.719307854538783e-05</v>
+        <v>0.0009033118840306997</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.977368659339845e-05</v>
+        <v>0.0001339995651505888</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002442709519527853</v>
+        <v>0.001380296191200614</v>
       </c>
       <c r="DT9" t="n">
-        <v>7.239053957164288e-05</v>
+        <v>0.001345328986644745</v>
       </c>
       <c r="DU9" t="n">
-        <v>1.850860644481145e-05</v>
+        <v>0.00232748594135046</v>
       </c>
       <c r="DV9" t="n">
-        <v>7.757174898870289e-05</v>
+        <v>0.005091058555990458</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001529233122710139</v>
+        <v>0.0001685819588601589</v>
       </c>
       <c r="DX9" t="n">
-        <v>4.46263984485995e-05</v>
+        <v>0.0003922969626728445</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0002908609458245337</v>
+        <v>0.002443706849589944</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001015876041492447</v>
+        <v>0.001483027823269367</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0002231372491223738</v>
+        <v>0.0003203086089342833</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0001028896949719638</v>
+        <v>0.003756401594728231</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.952678212546743e-05</v>
+        <v>0.0004553741309791803</v>
       </c>
       <c r="ED9" t="n">
-        <v>6.191922147991136e-05</v>
+        <v>0.0058229835703969</v>
       </c>
       <c r="EE9" t="n">
-        <v>2.289797157573048e-05</v>
+        <v>0.005511907394975424</v>
       </c>
       <c r="EF9" t="n">
-        <v>4.221743438392878e-05</v>
+        <v>0.00187676539644599</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0001474918681196868</v>
+        <v>0.002483424730598927</v>
       </c>
       <c r="EH9" t="n">
-        <v>1.185788005386712e-05</v>
+        <v>0.002201026305556297</v>
       </c>
       <c r="EI9" t="n">
-        <v>6.880508590256795e-05</v>
+        <v>0.003598254639655352</v>
       </c>
       <c r="EJ9" t="n">
-        <v>7.745707989670336e-05</v>
+        <v>0.0004025563830509782</v>
       </c>
       <c r="EK9" t="n">
-        <v>9.946606587618589e-05</v>
+        <v>0.001285964855924249</v>
       </c>
       <c r="EL9" t="n">
-        <v>9.584413783159107e-05</v>
+        <v>7.458525942638516e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>4.729223292088136e-05</v>
+        <v>0.000149341460200958</v>
       </c>
       <c r="EN9" t="n">
-        <v>9.634048183215782e-06</v>
+        <v>0.0003933839034289122</v>
       </c>
       <c r="EO9" t="n">
-        <v>9.148247772827744e-05</v>
+        <v>0.001016693888232112</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0002106080501107499</v>
+        <v>0.003891728352755308</v>
       </c>
       <c r="EQ9" t="n">
-        <v>2.520075213396922e-05</v>
+        <v>9.57750016823411e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001294906105613336</v>
+        <v>0.002980529796332121</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001497858029324561</v>
+        <v>0.0009355910588055849</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0004881607310380787</v>
+        <v>0.0007309167995117605</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0001789935922715813</v>
+        <v>0.001176249352283776</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0002055456134257838</v>
+        <v>0.001541538164019585</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.782213414320722e-06</v>
+        <v>0.003122274298220873</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0001000164484139532</v>
+        <v>1.370775862596929e-06</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0002686510269995779</v>
+        <v>0.004189301747828722</v>
       </c>
       <c r="EZ9" t="n">
-        <v>3.595216185203753e-05</v>
+        <v>0.0004142193356528878</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001156079961219802</v>
+        <v>0.004098375327885151</v>
       </c>
       <c r="FB9" t="n">
-        <v>1.275286194868386e-05</v>
+        <v>0.0001330910599790514</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001500622456660494</v>
+        <v>0.001678119646385312</v>
       </c>
       <c r="FD9" t="n">
-        <v>7.811730029061437e-05</v>
+        <v>0.0006987857632339001</v>
       </c>
       <c r="FE9" t="n">
-        <v>2.992819281644188e-05</v>
+        <v>0.001057653455063701</v>
       </c>
       <c r="FF9" t="n">
-        <v>7.693337101954967e-05</v>
+        <v>0.0008616075501777232</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.415987445507199e-05</v>
+        <v>0.0001324052864219993</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0001399301836499944</v>
+        <v>0.001691452111117542</v>
       </c>
       <c r="FI9" t="n">
-        <v>6.491695967270061e-05</v>
+        <v>0.0003693519392982125</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0001461436186218634</v>
+        <v>0.002100538462400436</v>
       </c>
       <c r="FK9" t="n">
-        <v>3.305522113805637e-05</v>
+        <v>0.001036627683788538</v>
       </c>
       <c r="FL9" t="n">
-        <v>5.714003782486543e-05</v>
+        <v>0.0001849461114034057</v>
       </c>
       <c r="FM9" t="n">
-        <v>2.010119351325557e-05</v>
+        <v>0.0008609537617303431</v>
       </c>
       <c r="FN9" t="n">
-        <v>6.714853952871636e-05</v>
+        <v>0.000132524233777076</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001289217034354806</v>
+        <v>0.0007194837089627981</v>
       </c>
       <c r="FP9" t="n">
-        <v>2.81819829979213e-05</v>
+        <v>0.001964270602911711</v>
       </c>
       <c r="FQ9" t="n">
-        <v>5.920386320212856e-05</v>
+        <v>0.004545619711279869</v>
       </c>
       <c r="FR9" t="n">
-        <v>2.879144085454755e-05</v>
+        <v>0.003137724474072456</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0002796005574055016</v>
+        <v>0.003683399874716997</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0002191731036873534</v>
+        <v>0.003963280469179153</v>
       </c>
       <c r="FU9" t="n">
-        <v>5.158065687282942e-05</v>
+        <v>0.001888585044071078</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0001138464358518831</v>
+        <v>0.0002182064345106483</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.014780355035327e-05</v>
+        <v>0.00515100359916687</v>
       </c>
       <c r="FX9" t="n">
-        <v>9.669059363659471e-05</v>
+        <v>0.002411902416497469</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0002637908328324556</v>
+        <v>0.001417208928614855</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001199489706777968</v>
+        <v>0.0005327838589437306</v>
       </c>
       <c r="GA9" t="n">
-        <v>4.421350604388863e-05</v>
+        <v>0.001226817141287029</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0001145424612332135</v>
+        <v>0.0036722959484905</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0001178060774691403</v>
+        <v>0.0005969226476736367</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0002776082546915859</v>
+        <v>0.002744783880189061</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0004539125366136432</v>
+        <v>0.002289187163114548</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.191838186467066e-05</v>
+        <v>0.001974968239665031</v>
       </c>
       <c r="GG9" t="n">
-        <v>5.026242433814332e-05</v>
+        <v>0.001366108655929565</v>
       </c>
     </row>
     <row r="10">
@@ -6120,2278 +6120,2278 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.774847074864638e-10</v>
+        <v>2.524315689811374e-08</v>
       </c>
       <c r="B11" t="n">
-        <v>1.726673665158884e-10</v>
+        <v>1.854238718124179e-07</v>
       </c>
       <c r="C11" t="n">
-        <v>7.630948650749758e-11</v>
+        <v>3.982932383905791e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>8.601739875935266e-10</v>
+        <v>4.26890593985263e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>1.049426032184719e-10</v>
+        <v>4.278619769593206e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>9.264601585901033e-11</v>
+        <v>7.20502839612891e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>3.959498701133768e-11</v>
+        <v>2.172687274537566e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>6.856931689114276e-11</v>
+        <v>3.561792993878043e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>4.582202672853697e-13</v>
+        <v>2.015026545620913e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.26672444703091e-10</v>
+        <v>1.337520849631346e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>9.941601014640256e-11</v>
+        <v>2.106646519450805e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>4.969029701595851e-11</v>
+        <v>6.806320129726373e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.465780995526302e-10</v>
+        <v>8.257697459157498e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>8.61288956821582e-11</v>
+        <v>8.525071848453081e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.575171270142619e-10</v>
+        <v>7.083897912707471e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>1.300781010682428e-10</v>
+        <v>3.204424725566923e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.119989266942014e-10</v>
+        <v>1.148199579859011e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>4.485330856729419e-11</v>
+        <v>3.831539885368329e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.432536810870189e-12</v>
+        <v>4.40344205543397e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>8.064366015247959e-12</v>
+        <v>9.544326218247079e-09</v>
       </c>
       <c r="U11" t="n">
-        <v>9.247821952662605e-11</v>
+        <v>2.888740979756221e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.820638258209772e-11</v>
+        <v>2.362185558268948e-09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.971986463011888e-10</v>
+        <v>1.167151708614256e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>9.605571546500435e-12</v>
+        <v>2.209086424898032e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.305227758154672e-10</v>
+        <v>4.193006830632839e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.353649716408285e-11</v>
+        <v>2.468943627320641e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68597330540976e-10</v>
+        <v>2.537809962177562e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.112964650995529e-10</v>
+        <v>1.105840974346961e-09</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.42390099711065e-10</v>
+        <v>2.904718954255259e-08</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.319328476640408e-11</v>
+        <v>1.530285942408227e-08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.426788825975578e-10</v>
+        <v>5.047839835015111e-08</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.59612650558239e-11</v>
+        <v>3.842125195774315e-08</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.546865496277917e-10</v>
+        <v>7.251054512380506e-08</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.504620453373633e-11</v>
+        <v>9.588962512907528e-09</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.60374449831302e-10</v>
+        <v>4.875820280858534e-08</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7.609776003780766e-11</v>
+        <v>6.666760921092418e-09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.036895131729555e-11</v>
+        <v>5.882845321991681e-09</v>
       </c>
       <c r="AL11" t="n">
-        <v>9.670891865098952e-11</v>
+        <v>4.851320412058158e-08</v>
       </c>
       <c r="AM11" t="n">
-        <v>9.015972690651353e-11</v>
+        <v>3.876990817275328e-08</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.064574107316311e-11</v>
+        <v>2.593019310381806e-08</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.820925216167169e-10</v>
+        <v>2.036366986146732e-08</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.271074356878898e-10</v>
+        <v>2.159822187763893e-08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.464720011945531e-10</v>
+        <v>2.270121157721405e-08</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.024473561539452e-10</v>
+        <v>1.770019464331085e-09</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01378294647958e-10</v>
+        <v>1.448625885913657e-09</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.173946324825266e-13</v>
+        <v>3.190713693257408e-09</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.957686262046067e-11</v>
+        <v>1.448941588932939e-07</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.119806050808307e-11</v>
+        <v>4.84555009450105e-08</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.299079425784669e-10</v>
+        <v>1.348278111379386e-08</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.099913629764586e-11</v>
+        <v>9.971542169751046e-08</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.1664432161066e-12</v>
+        <v>8.690599884175754e-08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.133554222709776e-10</v>
+        <v>3.263260772712329e-10</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.409204334450024e-11</v>
+        <v>1.443444830329099e-08</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.572462798333675e-10</v>
+        <v>2.860193859532956e-09</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.665989013410751e-10</v>
+        <v>1.596921173074861e-08</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.335534957242373e-11</v>
+        <v>2.976655189002031e-08</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.366138535103701e-11</v>
+        <v>3.312721830184273e-08</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.61026235348627e-11</v>
+        <v>2.106280927449689e-09</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.358779061488846e-11</v>
+        <v>6.069434732580703e-08</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.376813759170538e-11</v>
+        <v>5.118243162627323e-09</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.151407954038454e-11</v>
+        <v>1.02125667922337e-08</v>
       </c>
       <c r="BJ11" t="n">
-        <v>4.187980517933454e-10</v>
+        <v>4.399866782023309e-08</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.677868426477104e-11</v>
+        <v>1.24328050077338e-08</v>
       </c>
       <c r="BL11" t="n">
-        <v>5.712349343545142e-11</v>
+        <v>4.613963655586417e-10</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.643597643187562e-11</v>
+        <v>1.568460916701042e-09</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.630165778036655e-11</v>
+        <v>1.660881565612726e-08</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.076800523747146e-10</v>
+        <v>8.675842266825384e-09</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.466460008980874e-10</v>
+        <v>4.082808402472438e-08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.451874453994861e-10</v>
+        <v>7.049849592988267e-10</v>
       </c>
       <c r="BR11" t="n">
-        <v>3.363594472394205e-11</v>
+        <v>1.61451865210438e-08</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.533312969121848e-12</v>
+        <v>2.095801043822121e-08</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.881610393692171e-11</v>
+        <v>4.152409527335976e-09</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.346413605607388e-11</v>
+        <v>1.201606991685367e-08</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.194050843784545e-11</v>
+        <v>9.214208773755672e-08</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.381412601837329e-11</v>
+        <v>3.758761835115365e-08</v>
       </c>
       <c r="BX11" t="n">
-        <v>1.315093450804383e-10</v>
+        <v>1.026995288810895e-08</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.872397095847305e-11</v>
+        <v>1.481607503350801e-09</v>
       </c>
       <c r="BZ11" t="n">
-        <v>9.550171764516335e-11</v>
+        <v>4.46841887935534e-08</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.863982440619694e-10</v>
+        <v>3.864353459448466e-08</v>
       </c>
       <c r="CB11" t="n">
-        <v>7.563203535676521e-11</v>
+        <v>9.308571691235557e-09</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.861400616975928e-10</v>
+        <v>2.460427239725504e-08</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.398210962097693e-11</v>
+        <v>6.094044713300661e-10</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.865713833426597e-11</v>
+        <v>6.769749916202272e-08</v>
       </c>
       <c r="CF11" t="n">
-        <v>9.807540890527378e-11</v>
+        <v>1.751041089903538e-09</v>
       </c>
       <c r="CG11" t="n">
-        <v>9.248374288617356e-11</v>
+        <v>1.432751695062962e-08</v>
       </c>
       <c r="CH11" t="n">
-        <v>6.404383967595351e-11</v>
+        <v>1.775431179851239e-08</v>
       </c>
       <c r="CI11" t="n">
-        <v>3.070989990083817e-11</v>
+        <v>2.253778497163239e-08</v>
       </c>
       <c r="CJ11" t="n">
-        <v>3.491645861330994e-11</v>
+        <v>8.275637064514285e-09</v>
       </c>
       <c r="CK11" t="n">
-        <v>3.791282912612992e-11</v>
+        <v>5.421315396603177e-09</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.278323280562432e-10</v>
+        <v>3.169517093226659e-09</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.171112790077089e-10</v>
+        <v>5.417994231038392e-08</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.160457091004986e-10</v>
+        <v>1.043105868347993e-07</v>
       </c>
       <c r="CO11" t="n">
-        <v>5.466831154432583e-11</v>
+        <v>7.545952485088492e-08</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.451454039764656e-10</v>
+        <v>1.351048517506115e-08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>1.116957290547838e-10</v>
+        <v>2.220784445228219e-08</v>
       </c>
       <c r="CR11" t="n">
-        <v>2.08795827849606e-10</v>
+        <v>3.673350335020586e-08</v>
       </c>
       <c r="CS11" t="n">
-        <v>1.197369703387352e-10</v>
+        <v>3.524222336181992e-08</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.1824493040844e-10</v>
+        <v>1.214260914039755e-10</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.776742988846003e-11</v>
+        <v>4.201466730080483e-09</v>
       </c>
       <c r="CV11" t="n">
-        <v>4.426433525273055e-11</v>
+        <v>1.501671675896432e-09</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.113383079649367e-11</v>
+        <v>6.245246453318032e-08</v>
       </c>
       <c r="CX11" t="n">
-        <v>3.739584336637236e-11</v>
+        <v>8.465671719193324e-09</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.639642033257616e-10</v>
+        <v>1.960662743272223e-08</v>
       </c>
       <c r="CZ11" t="n">
-        <v>6.435535437887552e-11</v>
+        <v>2.649335684168364e-08</v>
       </c>
       <c r="DA11" t="n">
-        <v>5.556093779501836e-11</v>
+        <v>2.225720052706492e-08</v>
       </c>
       <c r="DB11" t="n">
-        <v>4.083711840907611e-11</v>
+        <v>1.243870428879745e-08</v>
       </c>
       <c r="DC11" t="n">
-        <v>4.298119152257307e-11</v>
+        <v>6.576086342136023e-09</v>
       </c>
       <c r="DD11" t="n">
-        <v>8.921552385743325e-11</v>
+        <v>1.068097255085831e-08</v>
       </c>
       <c r="DE11" t="n">
-        <v>3.273599447073394e-11</v>
+        <v>1.690378859109387e-08</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.128695136827119e-10</v>
+        <v>1.234275615047409e-08</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.959077037902659e-10</v>
+        <v>5.248516288247629e-09</v>
       </c>
       <c r="DH11" t="n">
-        <v>7.880975871898954e-10</v>
+        <v>1.778526481643894e-08</v>
       </c>
       <c r="DI11" t="n">
-        <v>3.227058620325352e-10</v>
+        <v>5.665591551462512e-09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>6.013239906010881e-11</v>
+        <v>8.916894955746102e-08</v>
       </c>
       <c r="DK11" t="n">
-        <v>1.283573768107171e-11</v>
+        <v>8.840699727841184e-09</v>
       </c>
       <c r="DL11" t="n">
-        <v>5.236794886620544e-10</v>
+        <v>5.99982215021555e-08</v>
       </c>
       <c r="DM11" t="n">
-        <v>1.546749534009351e-11</v>
+        <v>1.466916099701621e-08</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.649347151910785e-11</v>
+        <v>1.419440920358284e-08</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.694944705421531e-11</v>
+        <v>3.898234623989083e-08</v>
       </c>
       <c r="DP11" t="n">
-        <v>1.325150544850828e-10</v>
+        <v>4.813226262001535e-09</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5.653350704237781e-11</v>
+        <v>1.525466686302934e-08</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.757732816195741e-11</v>
+        <v>1.030536722623765e-08</v>
       </c>
       <c r="DS11" t="n">
-        <v>1.601885984969798e-10</v>
+        <v>9.005757917179835e-09</v>
       </c>
       <c r="DT11" t="n">
-        <v>2.201721617522967e-11</v>
+        <v>3.349655841589083e-08</v>
       </c>
       <c r="DU11" t="n">
-        <v>5.369863234627736e-11</v>
+        <v>7.242642041660474e-09</v>
       </c>
       <c r="DV11" t="n">
-        <v>2.889709860287581e-10</v>
+        <v>2.404612331474709e-08</v>
       </c>
       <c r="DW11" t="n">
-        <v>1.250624187543181e-10</v>
+        <v>6.264030960601019e-10</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.393549685368978e-11</v>
+        <v>2.83536216727498e-08</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.139269872358796e-10</v>
+        <v>2.615612970657821e-08</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.649715334981153e-11</v>
+        <v>3.129690950842701e-09</v>
       </c>
       <c r="EA11" t="n">
-        <v>1.094169893578467e-10</v>
+        <v>4.8882640157899e-08</v>
       </c>
       <c r="EB11" t="n">
-        <v>2.715712932310765e-10</v>
+        <v>4.30305462373326e-08</v>
       </c>
       <c r="EC11" t="n">
-        <v>6.786630979416231e-11</v>
+        <v>2.35127961545345e-09</v>
       </c>
       <c r="ED11" t="n">
-        <v>5.570290409484535e-11</v>
+        <v>5.503622801938945e-08</v>
       </c>
       <c r="EE11" t="n">
-        <v>1.726142319358193e-11</v>
+        <v>6.810640229559795e-08</v>
       </c>
       <c r="EF11" t="n">
-        <v>2.626534753580323e-11</v>
+        <v>2.668138154859889e-09</v>
       </c>
       <c r="EG11" t="n">
-        <v>2.366974498346774e-11</v>
+        <v>2.405411692052439e-08</v>
       </c>
       <c r="EH11" t="n">
-        <v>6.084661247074408e-11</v>
+        <v>3.010124061120223e-08</v>
       </c>
       <c r="EI11" t="n">
-        <v>7.852890560045012e-11</v>
+        <v>1.484098088866403e-08</v>
       </c>
       <c r="EJ11" t="n">
-        <v>4.339915926632187e-11</v>
+        <v>2.18818403396881e-08</v>
       </c>
       <c r="EK11" t="n">
-        <v>4.923690968827721e-11</v>
+        <v>2.103549867626953e-08</v>
       </c>
       <c r="EL11" t="n">
-        <v>6.414248993058536e-11</v>
+        <v>1.690782092111931e-08</v>
       </c>
       <c r="EM11" t="n">
-        <v>1.276027807722846e-11</v>
+        <v>6.926643258964305e-09</v>
       </c>
       <c r="EN11" t="n">
-        <v>7.8795442393087e-11</v>
+        <v>2.068067672666984e-08</v>
       </c>
       <c r="EO11" t="n">
-        <v>3.929590680629147e-11</v>
+        <v>7.987992489688622e-09</v>
       </c>
       <c r="EP11" t="n">
-        <v>1.306781072241137e-10</v>
+        <v>5.267354907800836e-08</v>
       </c>
       <c r="EQ11" t="n">
-        <v>9.110329157735464e-11</v>
+        <v>1.393481241507288e-08</v>
       </c>
       <c r="ER11" t="n">
-        <v>2.866486562003168e-11</v>
+        <v>8.86313245018755e-12</v>
       </c>
       <c r="ES11" t="n">
-        <v>2.659047149133897e-10</v>
+        <v>1.518261782962327e-08</v>
       </c>
       <c r="ET11" t="n">
-        <v>1.051480430502849e-10</v>
+        <v>1.14903766501584e-08</v>
       </c>
       <c r="EU11" t="n">
-        <v>3.271150711414705e-11</v>
+        <v>3.600298725814355e-09</v>
       </c>
       <c r="EV11" t="n">
-        <v>2.512785535202511e-10</v>
+        <v>7.251239608763171e-09</v>
       </c>
       <c r="EW11" t="n">
-        <v>8.587446032048973e-11</v>
+        <v>2.590108039157712e-08</v>
       </c>
       <c r="EX11" t="n">
-        <v>5.159475624516574e-11</v>
+        <v>5.695173777020557e-10</v>
       </c>
       <c r="EY11" t="n">
-        <v>8.061976433659801e-12</v>
+        <v>6.955012565867946e-08</v>
       </c>
       <c r="EZ11" t="n">
-        <v>6.989597095552469e-11</v>
+        <v>6.738251734361711e-09</v>
       </c>
       <c r="FA11" t="n">
-        <v>1.21648247031203e-10</v>
+        <v>1.787486603177513e-08</v>
       </c>
       <c r="FB11" t="n">
-        <v>4.552332122376157e-11</v>
+        <v>1.382921599457632e-08</v>
       </c>
       <c r="FC11" t="n">
-        <v>3.442663515373923e-11</v>
+        <v>2.068257565213116e-08</v>
       </c>
       <c r="FD11" t="n">
-        <v>4.730331057412052e-11</v>
+        <v>7.491091080780166e-11</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.377358553073972e-11</v>
+        <v>5.394458213459075e-09</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.198158100512714e-10</v>
+        <v>1.819633155264455e-08</v>
       </c>
       <c r="FG11" t="n">
-        <v>6.080588116352814e-11</v>
+        <v>1.458507803420162e-08</v>
       </c>
       <c r="FH11" t="n">
-        <v>1.181131303873428e-10</v>
+        <v>1.735809540548416e-08</v>
       </c>
       <c r="FI11" t="n">
-        <v>2.288662592775381e-10</v>
+        <v>2.705626833687802e-09</v>
       </c>
       <c r="FJ11" t="n">
-        <v>2.022118444910959e-10</v>
+        <v>1.799228854793e-08</v>
       </c>
       <c r="FK11" t="n">
-        <v>1.366796814616933e-10</v>
+        <v>6.602558055845975e-09</v>
       </c>
       <c r="FL11" t="n">
-        <v>2.919416791646867e-11</v>
+        <v>2.081380223728502e-08</v>
       </c>
       <c r="FM11" t="n">
-        <v>1.522046655377807e-10</v>
+        <v>1.604389687770436e-08</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.17612697358993e-10</v>
+        <v>2.151749001200187e-08</v>
       </c>
       <c r="FO11" t="n">
-        <v>3.491849864811769e-11</v>
+        <v>4.195007363705372e-08</v>
       </c>
       <c r="FP11" t="n">
-        <v>6.487600734406129e-11</v>
+        <v>3.453143193610231e-08</v>
       </c>
       <c r="FQ11" t="n">
-        <v>1.629115245482815e-12</v>
+        <v>6.666926566367692e-08</v>
       </c>
       <c r="FR11" t="n">
-        <v>3.190250841278441e-11</v>
+        <v>3.338444543032892e-08</v>
       </c>
       <c r="FS11" t="n">
-        <v>3.797259034987732e-11</v>
+        <v>2.24986607122446e-08</v>
       </c>
       <c r="FT11" t="n">
-        <v>1.124582232892024e-10</v>
+        <v>6.61129888612777e-08</v>
       </c>
       <c r="FU11" t="n">
-        <v>5.383082174459375e-11</v>
+        <v>2.758624439991308e-08</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.614599509120907e-11</v>
+        <v>3.321217079133021e-08</v>
       </c>
       <c r="FW11" t="n">
-        <v>6.428007431891203e-12</v>
+        <v>2.774346796741156e-08</v>
       </c>
       <c r="FX11" t="n">
-        <v>4.569988051178475e-12</v>
+        <v>1.660902171352063e-08</v>
       </c>
       <c r="FY11" t="n">
-        <v>1.489395967668727e-10</v>
+        <v>1.686064510231233e-09</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.402003235728699e-10</v>
+        <v>1.459563669925501e-08</v>
       </c>
       <c r="GA11" t="n">
-        <v>5.938000091632034e-11</v>
+        <v>1.121332360298766e-08</v>
       </c>
       <c r="GB11" t="n">
-        <v>6.468682794275038e-12</v>
+        <v>2.373863061677639e-08</v>
       </c>
       <c r="GC11" t="n">
-        <v>1.305323765743438e-10</v>
+        <v>1.902880519821792e-09</v>
       </c>
       <c r="GD11" t="n">
-        <v>3.780142865394964e-11</v>
+        <v>4.284326138304095e-08</v>
       </c>
       <c r="GE11" t="n">
-        <v>3.444475260572233e-10</v>
+        <v>5.016393345158576e-08</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.481323119723044e-10</v>
+        <v>5.385138557301161e-09</v>
       </c>
       <c r="GG11" t="n">
-        <v>2.113133418246704e-10</v>
+        <v>3.111205515438087e-08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0002604331530164927</v>
+        <v>0.0007177041843533516</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001660062931478024</v>
+        <v>0.02713383734226227</v>
       </c>
       <c r="C12" t="n">
-        <v>6.651979492744431e-05</v>
+        <v>0.01757293753325939</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008850174490362406</v>
+        <v>0.01173534151166677</v>
       </c>
       <c r="E12" t="n">
-        <v>6.145401857793331e-05</v>
+        <v>0.01645819284021854</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001480439677834511</v>
+        <v>0.03250168636441231</v>
       </c>
       <c r="G12" t="n">
-        <v>5.837149365106598e-05</v>
+        <v>0.005419558379799128</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002766400284599513</v>
+        <v>0.02274600975215435</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001205522348755039</v>
+        <v>0.002489428734406829</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0003750566975213587</v>
+        <v>0.002255279570817947</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001378772314637899</v>
+        <v>0.06503370404243469</v>
       </c>
       <c r="L12" t="n">
-        <v>6.708537694066763e-05</v>
+        <v>0.0131165087223053</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0009362052660435438</v>
+        <v>0.00863195862621069</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0001405906659783795</v>
+        <v>0.03045442886650562</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00148351676762104</v>
+        <v>0.04305170103907585</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001717457344057038</v>
+        <v>0.0200317744165659</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.726692426018417e-05</v>
+        <v>0.001047845697030425</v>
       </c>
       <c r="R12" t="n">
-        <v>9.732496982906014e-05</v>
+        <v>0.00915799755603075</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001025252640829422</v>
+        <v>0.008339914493262768</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0002459709940012544</v>
+        <v>0.0006416793912649155</v>
       </c>
       <c r="U12" t="n">
-        <v>2.064443833660334e-07</v>
+        <v>0.002186814555898309</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0002349505957681686</v>
+        <v>0.01271499134600163</v>
       </c>
       <c r="W12" t="n">
-        <v>6.716658390359953e-05</v>
+        <v>0.01379647850990295</v>
       </c>
       <c r="X12" t="n">
-        <v>2.123889134963974e-05</v>
+        <v>0.009028872475028038</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0001111570600187406</v>
+        <v>0.007087830919772387</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.440048648277298e-06</v>
+        <v>0.02497799508273602</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001796883443603292</v>
+        <v>0.00661475770175457</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.715649993158877e-05</v>
+        <v>0.0208719577640295</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0001541853416711092</v>
+        <v>0.002446669153869152</v>
       </c>
       <c r="AD12" t="n">
-        <v>7.547512359451503e-05</v>
+        <v>0.008146744221448898</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001584462297614664</v>
+        <v>0.001115363440476358</v>
       </c>
       <c r="AF12" t="n">
-        <v>4.400765465106815e-05</v>
+        <v>0.03239766135811806</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.171446173335426e-05</v>
+        <v>0.0036106260959059</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0002922421554103494</v>
+        <v>0.01295360177755356</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.738860535435379e-05</v>
+        <v>0.02688544429838657</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.241370622068644e-05</v>
+        <v>0.003276215167716146</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001746597117744386</v>
+        <v>0.00580526189878583</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0002494444197509438</v>
+        <v>0.002889998955652118</v>
       </c>
       <c r="AM12" t="n">
-        <v>8.002412505447865e-05</v>
+        <v>0.005345340352505445</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.546274380525574e-05</v>
+        <v>0.00501971784979105</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.613904350961093e-05</v>
+        <v>0.009801280684769154</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.000245173490839079</v>
+        <v>0.002380973659455776</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001286412007175386</v>
+        <v>0.006610042415559292</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.950253499671817e-05</v>
+        <v>0.02058379538357258</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001606988080311567</v>
+        <v>0.003223673207685351</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0002528015756979585</v>
+        <v>0.003280889475718141</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001266594743356109</v>
+        <v>0.05873343348503113</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001425498339813203</v>
+        <v>0.00959528423845768</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0001566908613312989</v>
+        <v>0.008456985466182232</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0003451613301876932</v>
+        <v>0.01884024776518345</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0007440198678523302</v>
+        <v>0.03687097877264023</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0001451189164072275</v>
+        <v>0.003138713072985411</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0002617205027490854</v>
+        <v>0.006107279099524021</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0002012876211665571</v>
+        <v>0.00515297707170248</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001927924167830497</v>
+        <v>0.01183657441288233</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0003194980672560632</v>
+        <v>0.006452912464737892</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0003961033944506198</v>
+        <v>0.002173872664570808</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.000448762031737715</v>
+        <v>0.007598418742418289</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0005152715020813048</v>
+        <v>0.008220684714615345</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0005708853132091463</v>
+        <v>0.00702309887856245</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.655704884091392e-05</v>
+        <v>0.007765139453113079</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0003353726642671973</v>
+        <v>0.02392943948507309</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.480764593812637e-05</v>
+        <v>0.008538380265235901</v>
       </c>
       <c r="BL12" t="n">
-        <v>8.866811549523845e-05</v>
+        <v>0.008077230304479599</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0004013545403722674</v>
+        <v>0.02517247013747692</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001040540300891735</v>
+        <v>0.00319651747122407</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0003669765428639948</v>
+        <v>0.0125140342861414</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0003132672281935811</v>
+        <v>0.01677883788943291</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.107226338121109e-06</v>
+        <v>0.0001273037341888994</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0002570191281847656</v>
+        <v>0.002904258668422699</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.029626042116433e-05</v>
+        <v>0.01543673500418663</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.414385719224811e-05</v>
+        <v>0.001676761079579592</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0001216333475895226</v>
+        <v>0.003391305450350046</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0006203593802638352</v>
+        <v>0.03019963204860687</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.085572876036167e-08</v>
+        <v>0.003548307809978724</v>
       </c>
       <c r="BX12" t="n">
-        <v>4.784129487234168e-05</v>
+        <v>0.01576042547821999</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.939406815334223e-05</v>
+        <v>0.01128065958619118</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001333430700469762</v>
+        <v>0.01437634229660034</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0002342527877772227</v>
+        <v>0.004712292458862066</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0001548231521155685</v>
+        <v>0.01287583261728287</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001627870806260034</v>
+        <v>0.002085806801915169</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.934180858777836e-05</v>
+        <v>0.009131354279816151</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003175743040628731</v>
+        <v>0.01024176646023989</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001295849069720134</v>
+        <v>0.006589442025870085</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0001821978075895458</v>
+        <v>0.0004583165573421866</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0001147993971244432</v>
+        <v>0.007714952807873487</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0002603350149001926</v>
+        <v>0.01295460481196642</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.783636490581557e-05</v>
+        <v>0.004258214496076107</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.856555172707886e-05</v>
+        <v>0.002559380838647485</v>
       </c>
       <c r="CL12" t="n">
-        <v>9.81505581876263e-05</v>
+        <v>0.002029038034379482</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0002454123459756374</v>
+        <v>0.002586400136351585</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002099352423101664</v>
+        <v>0.03698763623833656</v>
       </c>
       <c r="CO12" t="n">
-        <v>4.348433139966801e-05</v>
+        <v>0.004089318215847015</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0002421570825390518</v>
+        <v>0.02304987236857414</v>
       </c>
       <c r="CQ12" t="n">
-        <v>8.676296420162544e-05</v>
+        <v>0.01148730516433716</v>
       </c>
       <c r="CR12" t="n">
-        <v>2.678458258742467e-05</v>
+        <v>0.01441608741879463</v>
       </c>
       <c r="CS12" t="n">
-        <v>4.322004315326922e-05</v>
+        <v>0.01014673430472612</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0002076459059026092</v>
+        <v>0.0002899126848205924</v>
       </c>
       <c r="CU12" t="n">
-        <v>5.697711094398983e-05</v>
+        <v>0.002826898824423552</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.945233998412732e-05</v>
+        <v>0.007095723412930965</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002406459971098229</v>
+        <v>0.008721835911273956</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001061745133483782</v>
+        <v>0.005147452931851149</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0002581325243227184</v>
+        <v>0.002767119323834777</v>
       </c>
       <c r="CZ12" t="n">
-        <v>7.903379446361214e-05</v>
+        <v>0.004132093861699104</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0002423120167804882</v>
+        <v>0.01295475475490093</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0001081159207387827</v>
+        <v>0.0007477838662452996</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001418528845533729</v>
+        <v>0.004063940141350031</v>
       </c>
       <c r="DD12" t="n">
-        <v>5.19130117027089e-05</v>
+        <v>0.004289665725082159</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.000135701586259529</v>
+        <v>0.01081765536218882</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0005586037295870483</v>
+        <v>0.007710089907050133</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.514932152233087e-05</v>
+        <v>0.02082560025155544</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0004104810650460422</v>
+        <v>0.01739304885268211</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0001044502932927571</v>
+        <v>0.02171801589429379</v>
       </c>
       <c r="DJ12" t="n">
-        <v>5.613958273897879e-05</v>
+        <v>0.002032240852713585</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0003330562612973154</v>
+        <v>0.01566982083022594</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0003080603200942278</v>
+        <v>0.002840653294697404</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.000207724588108249</v>
+        <v>0.002193099353462458</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001522573438705876</v>
+        <v>0.008900490589439869</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001600317191332579</v>
+        <v>0.01519665494561195</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001915666653076187</v>
+        <v>0.001154945697635412</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0003154341829940677</v>
+        <v>0.01317218504846096</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.005897037335671e-05</v>
+        <v>0.01686766743659973</v>
       </c>
       <c r="DS12" t="n">
-        <v>2.507666795281693e-05</v>
+        <v>0.002944610081613064</v>
       </c>
       <c r="DT12" t="n">
-        <v>1.790030000847764e-05</v>
+        <v>0.003752220189198852</v>
       </c>
       <c r="DU12" t="n">
-        <v>3.611654392443597e-05</v>
+        <v>0.02844442427158356</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001334886765107512</v>
+        <v>0.00287189893424511</v>
       </c>
       <c r="DW12" t="n">
-        <v>2.088624387397431e-05</v>
+        <v>0.01303072366863489</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.888238875835668e-05</v>
+        <v>0.007367003709077835</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0001305212790612131</v>
+        <v>0.008971930481493473</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.946182939922437e-05</v>
+        <v>0.003400762099772692</v>
       </c>
       <c r="EA12" t="n">
-        <v>5.527559915208258e-05</v>
+        <v>0.001050564227625728</v>
       </c>
       <c r="EB12" t="n">
-        <v>7.33380948076956e-05</v>
+        <v>0.01639197766780853</v>
       </c>
       <c r="EC12" t="n">
-        <v>5.737891115131788e-06</v>
+        <v>0.002451960230246186</v>
       </c>
       <c r="ED12" t="n">
-        <v>3.156361344736069e-05</v>
+        <v>0.007414503488689661</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0001139950400101952</v>
+        <v>0.0118528213351965</v>
       </c>
       <c r="EF12" t="n">
-        <v>8.087965397862718e-05</v>
+        <v>0.006337425205856562</v>
       </c>
       <c r="EG12" t="n">
-        <v>9.315184433944523e-05</v>
+        <v>0.005950721446424723</v>
       </c>
       <c r="EH12" t="n">
-        <v>2.390327063039877e-05</v>
+        <v>0.005864216014742851</v>
       </c>
       <c r="EI12" t="n">
-        <v>6.582539208466187e-05</v>
+        <v>0.009056712500751019</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0001037644542520866</v>
+        <v>0.004434596281498671</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0001915564062073827</v>
+        <v>0.01366602256894112</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0001423837529728189</v>
+        <v>0.002333737211301923</v>
       </c>
       <c r="EM12" t="n">
-        <v>4.259170236764476e-05</v>
+        <v>0.007339415140450001</v>
       </c>
       <c r="EN12" t="n">
-        <v>7.497717888327315e-05</v>
+        <v>0.004089240450412035</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0001492214214522392</v>
+        <v>0.004087207373231649</v>
       </c>
       <c r="EP12" t="n">
-        <v>9.907320782076567e-05</v>
+        <v>0.0008891699835658073</v>
       </c>
       <c r="EQ12" t="n">
-        <v>4.889783303951845e-05</v>
+        <v>0.004202554933726788</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001094239487429149</v>
+        <v>0.01003076229244471</v>
       </c>
       <c r="ES12" t="n">
-        <v>4.580825043376535e-05</v>
+        <v>0.003785496111959219</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0003501644532661885</v>
+        <v>0.004275294952094555</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001140184176620096</v>
+        <v>0.00640028016641736</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0001892761356430128</v>
+        <v>0.0009394584922119975</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.982333196792752e-05</v>
+        <v>0.00583572406321764</v>
       </c>
       <c r="EX12" t="n">
-        <v>2.787281846394762e-05</v>
+        <v>0.008875073865056038</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0002219843299826607</v>
+        <v>0.01158079598098993</v>
       </c>
       <c r="EZ12" t="n">
-        <v>5.45491129742004e-05</v>
+        <v>0.005790494382381439</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001736406702548265</v>
+        <v>1.920807699207217e-05</v>
       </c>
       <c r="FB12" t="n">
-        <v>8.751214772928506e-05</v>
+        <v>0.003856662660837173</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0002405312698101625</v>
+        <v>0.01369359437376261</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001185969813377596</v>
+        <v>0.005700338631868362</v>
       </c>
       <c r="FE12" t="n">
-        <v>1.919395072036423e-05</v>
+        <v>0.0002304065710632131</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0001269115164177492</v>
+        <v>0.004565093666315079</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0001003931538434699</v>
+        <v>0.008477297611534595</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001715344260446727</v>
+        <v>0.001405069138854742</v>
       </c>
       <c r="FI12" t="n">
-        <v>6.542187475133687e-05</v>
+        <v>0.0006719091907143593</v>
       </c>
       <c r="FJ12" t="n">
-        <v>6.901176675455645e-05</v>
+        <v>0.01261657662689686</v>
       </c>
       <c r="FK12" t="n">
-        <v>2.874253914342262e-05</v>
+        <v>0.00397211592644453</v>
       </c>
       <c r="FL12" t="n">
-        <v>8.015885396162048e-05</v>
+        <v>0.004241751972585917</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.71800893440377e-05</v>
+        <v>0.01056274864822626</v>
       </c>
       <c r="FN12" t="n">
-        <v>3.40883489116095e-05</v>
+        <v>0.01926427893340588</v>
       </c>
       <c r="FO12" t="n">
-        <v>4.496003020904027e-05</v>
+        <v>0.004071108531206846</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.000184750446351245</v>
+        <v>0.007323115132749081</v>
       </c>
       <c r="FQ12" t="n">
-        <v>4.34481116826646e-05</v>
+        <v>0.01574864611029625</v>
       </c>
       <c r="FR12" t="n">
-        <v>6.864908300485695e-06</v>
+        <v>0.01521262340247631</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0001602564589120448</v>
+        <v>0.01096479594707489</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0007266367319971323</v>
+        <v>0.008020889945328236</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0001876603928394616</v>
+        <v>0.0119487326592207</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0001022360156639479</v>
+        <v>0.0131121464073658</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0002137887058779597</v>
+        <v>0.006940804421901703</v>
       </c>
       <c r="FX12" t="n">
-        <v>1.783423067536205e-05</v>
+        <v>0.009361072443425655</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.000176468282006681</v>
+        <v>0.006102483719587326</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0001986189890885726</v>
+        <v>0.01046179048717022</v>
       </c>
       <c r="GA12" t="n">
-        <v>2.638451042002998e-05</v>
+        <v>0.001381405163556337</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0002201545430580154</v>
+        <v>0.008845868520438671</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.000119418793474324</v>
+        <v>0.007943139411509037</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001607225422048941</v>
+        <v>0.00234927493147552</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0004817972076125443</v>
+        <v>0.001530423993244767</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0002362199884373695</v>
+        <v>0.007184091955423355</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001478980702813715</v>
+        <v>0.01577983982861042</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.001940644928254187</v>
+        <v>1.099130440707086e-05</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0007836328586563468</v>
+        <v>5.720159970223904e-05</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005424166098237038</v>
+        <v>0.0001324637414654717</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004241309594362974</v>
+        <v>0.0001387688389513642</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003430936019867659</v>
+        <v>2.791815131786279e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001347145065665245</v>
+        <v>6.372737698256969e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001512803602963686</v>
+        <v>2.403101098025218e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0004483723314478993</v>
+        <v>5.346528632799163e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00147357489913702</v>
+        <v>9.417269757250324e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001678086933679879</v>
+        <v>2.133668749593198e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0006897248676978052</v>
+        <v>5.689341196557507e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004336296580731869</v>
+        <v>0.0001695616665529087</v>
       </c>
       <c r="M13" t="n">
-        <v>0.004481583368033171</v>
+        <v>0.0001846233499236405</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0008620326989330351</v>
+        <v>2.882469925680198e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001032154308632016</v>
+        <v>8.177090785466135e-05</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000973094895016402</v>
+        <v>1.540605808258988e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.907615508884192e-05</v>
+        <v>0.0001041938958223909</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00223807105794549</v>
+        <v>4.839649045607075e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0005754177691414952</v>
+        <v>1.519987199571915e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0009735169587656856</v>
+        <v>6.063885393814417e-07</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0009001068538054824</v>
+        <v>2.932640563813038e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0008529489277862012</v>
+        <v>2.448724262649193e-05</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0005921403062529862</v>
+        <v>2.68568310275441e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003384758601896465</v>
+        <v>4.163610719842836e-05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0006150910048745573</v>
+        <v>1.871596759883687e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.000615636061411351</v>
+        <v>7.964774340507574e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001165692301583476</v>
+        <v>3.962816117564216e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001733011798933148</v>
+        <v>2.344062886550091e-05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0004186437872704118</v>
+        <v>2.277366729686037e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001725502515910193</v>
+        <v>9.794449397304561e-06</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.00169046560768038</v>
+        <v>7.010393164819106e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001229697256349027</v>
+        <v>6.229547580005601e-06</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.100642738398165e-05</v>
+        <v>1.184870870929444e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0001107537827920169</v>
+        <v>1.40674728754675e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0007400678587146103</v>
+        <v>4.515060936682858e-05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0008735440205782652</v>
+        <v>2.742710603342857e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0005085358279757202</v>
+        <v>8.859172339725774e-06</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.867701161652803e-05</v>
+        <v>2.631024472066201e-06</v>
       </c>
       <c r="AM13" t="n">
-        <v>2.867559669539332e-05</v>
+        <v>3.531724723870866e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0002893874188885093</v>
+        <v>2.712251807679422e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001079939771443605</v>
+        <v>5.002557372790761e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.000205748830921948</v>
+        <v>1.03146394394571e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0004582849214784801</v>
+        <v>2.461667281750124e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001277374685741961</v>
+        <v>2.438227602397092e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003384562442079186</v>
+        <v>4.099097714060917e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001672412035986781</v>
+        <v>3.405331517569721e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.00197251420468092</v>
+        <v>1.099890141631477e-05</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.002881304826587439</v>
+        <v>0.0001666581956669688</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.003587491344660521</v>
+        <v>0.0001172565171145834</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0007278397097252309</v>
+        <v>4.430571607372258e-06</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0008510386687703431</v>
+        <v>9.110024257097393e-05</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.001072114333510399</v>
+        <v>8.399052603635937e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001039177644997835</v>
+        <v>3.49062102031894e-05</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0005490191979333758</v>
+        <v>7.620284304721281e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.001466139918193221</v>
+        <v>3.924167685909197e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.002806621138006449</v>
+        <v>1.905474891827907e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0008888319716788828</v>
+        <v>2.491673876647837e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.001535905874334276</v>
+        <v>2.267203672090545e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001382606336846948</v>
+        <v>1.348567002423806e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.002156517235562205</v>
+        <v>4.339770384831354e-05</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.001204599859192967</v>
+        <v>6.738088268321007e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0003912892425432801</v>
+        <v>5.854096889379434e-05</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001732073491439223</v>
+        <v>4.983721373719163e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001554047630634159</v>
+        <v>4.525789336184971e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0005930118495598435</v>
+        <v>4.597762745106593e-05</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.000785736832767725</v>
+        <v>4.614862064045155e-06</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.825109838042408e-05</v>
+        <v>3.007615305250511e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0006493370165117085</v>
+        <v>4.542525130091235e-05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0002448419691063464</v>
+        <v>9.140408110397402e-06</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0001440444320905954</v>
+        <v>6.51135815132875e-06</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0007715169922448695</v>
+        <v>7.487426046282053e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0003543170751072466</v>
+        <v>1.439306106476579e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0004338709404692054</v>
+        <v>9.487785064266063e-07</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001227831817232072</v>
+        <v>2.74575904768426e-05</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.002005850663408637</v>
+        <v>9.847685578279197e-05</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.002415986265987158</v>
+        <v>0.0001122180983657017</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.001138628693297505</v>
+        <v>9.896532901620958e-06</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003573236172087491</v>
+        <v>3.770732291741297e-05</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0003665828844532371</v>
+        <v>2.378767021582462e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0007240429986268282</v>
+        <v>2.357462108193431e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0008754605078138411</v>
+        <v>4.704228922491893e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0006133487331680954</v>
+        <v>3.083988303842489e-06</v>
       </c>
       <c r="CE13" t="n">
-        <v>4.437251482158899e-05</v>
+        <v>1.107646494347136e-05</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.001316740992479026</v>
+        <v>4.507420453592204e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0007441614870913327</v>
+        <v>5.363755190046504e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.000746953533962369</v>
+        <v>1.142978908319492e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002855350612662733</v>
+        <v>2.229360507044476e-05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0004948971327394247</v>
+        <v>4.327043825469445e-07</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0004280165303498507</v>
+        <v>7.715739229752216e-06</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001784911000868306</v>
+        <v>1.168660583061865e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001911562983877957</v>
+        <v>5.964472620689776e-06</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001580640207976103</v>
+        <v>9.476817467657384e-06</v>
       </c>
       <c r="CO13" t="n">
-        <v>2.92710610665381e-05</v>
+        <v>6.332717020995915e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0008086480665951967</v>
+        <v>0.0001034233573591337</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0003918526053894311</v>
+        <v>5.630079613183625e-06</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0005399271030910313</v>
+        <v>4.877299579675309e-05</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.00044848961988464</v>
+        <v>9.532341209705919e-06</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001906434074044228</v>
+        <v>1.301439806411508e-05</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0004118373326491565</v>
+        <v>3.457091224845499e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0004684184968937188</v>
+        <v>6.332266366371186e-06</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0004318640858400613</v>
+        <v>2.570451033534482e-05</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0009292477043345571</v>
+        <v>3.771765841520391e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0008315108134411275</v>
+        <v>4.768371945829131e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0004088668792974204</v>
+        <v>1.459755003452301e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001586735888849944</v>
+        <v>3.346794619574212e-05</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0004803854390047491</v>
+        <v>3.494254997349344e-06</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0003265505947638303</v>
+        <v>7.989102414285298e-06</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0001124227856053039</v>
+        <v>1.322018670180114e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0002241733891423792</v>
+        <v>4.721074219560251e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.001710825366899371</v>
+        <v>4.664241714635864e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.002068309113383293</v>
+        <v>1.087081182049587e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004453820001799613</v>
+        <v>2.236322688986547e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0002310526906512678</v>
+        <v>1.892960790428333e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001297011040151119</v>
+        <v>1.416260147379944e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001772144809365273</v>
+        <v>5.241924736765213e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0005076058441773057</v>
+        <v>4.786717545357533e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0005948789184913039</v>
+        <v>5.743162182625383e-05</v>
       </c>
       <c r="DN13" t="n">
-        <v>7.137792999856174e-05</v>
+        <v>1.433476427337155e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001346036093309522</v>
+        <v>1.000995234790025e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0009215110912919044</v>
+        <v>2.273634163429961e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0001947935670614243</v>
+        <v>1.602605334483087e-05</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001768043846823275</v>
+        <v>3.890263542416506e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0008334890007972717</v>
+        <v>1.236525167769287e-05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0007154096383601427</v>
+        <v>2.231250255135819e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>3.906944766640663e-05</v>
+        <v>1.757072459440678e-05</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001289713196456432</v>
+        <v>2.992382542288397e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0003930206003133208</v>
+        <v>6.290668534347787e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001803657622076571</v>
+        <v>4.141372119192965e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0004864934307988733</v>
+        <v>1.864131263573654e-05</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0003506617795210332</v>
+        <v>1.073169414667063e-06</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0009895735420286655</v>
+        <v>3.583068246371113e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.000986642437055707</v>
+        <v>4.357660873210989e-05</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.693246667855419e-05</v>
+        <v>1.933855492097791e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0004159039235673845</v>
+        <v>3.33259449689649e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001954190811375156</v>
+        <v>1.937611159519292e-05</v>
       </c>
       <c r="EF13" t="n">
-        <v>7.124655530788004e-05</v>
+        <v>3.124224531347863e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0005429349257610738</v>
+        <v>2.232270344393328e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001388640492223203</v>
+        <v>1.78974587470293e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001580947078764439</v>
+        <v>6.751615728717297e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>1.106459967559204e-05</v>
+        <v>1.967227763088886e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>2.320178646186832e-05</v>
+        <v>6.349993782350793e-06</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0005255861324258149</v>
+        <v>1.127610971707327e-06</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001049562415573746</v>
+        <v>5.117483397043543e-07</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0006203787634149194</v>
+        <v>8.616607374278829e-07</v>
       </c>
       <c r="EO13" t="n">
-        <v>5.860271630808711e-05</v>
+        <v>9.937805316440063e-07</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.001268016174435616</v>
+        <v>2.699035030673258e-05</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0006558119785040617</v>
+        <v>1.911696017486975e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0009180654305964708</v>
+        <v>3.350668339408003e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0006899108993820846</v>
+        <v>1.035020977724344e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.000164582539582625</v>
+        <v>5.737128230975941e-05</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0006550580728799105</v>
+        <v>9.196170140057802e-06</v>
       </c>
       <c r="EV13" t="n">
-        <v>6.432411464629695e-05</v>
+        <v>4.48706814495381e-05</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.000890774535946548</v>
+        <v>1.346644876321079e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.000478508765809238</v>
+        <v>5.372919531509979e-08</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0005411448073573411</v>
+        <v>1.564812191645615e-05</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.001244725310243666</v>
+        <v>4.407982851262204e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0007857878226786852</v>
+        <v>6.431840301956981e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0005293726571835577</v>
+        <v>1.151941614807583e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>8.86127381818369e-05</v>
+        <v>2.88915507553611e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0004357514262665063</v>
+        <v>4.42221607954707e-06</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0003281071549281478</v>
+        <v>2.301033964613453e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0003445648471824825</v>
+        <v>1.558310577820521e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001804527564672753</v>
+        <v>1.231563237524824e-05</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0009862004080787301</v>
+        <v>2.701280027395114e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>1.843195059336722e-05</v>
+        <v>1.319254261034075e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0007936906768009067</v>
+        <v>3.103630660916679e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0003930855600629002</v>
+        <v>2.504929943825118e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0006974975694902241</v>
+        <v>3.990684490418062e-05</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0004099537909496576</v>
+        <v>9.57827978709247e-07</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0007143021794036031</v>
+        <v>7.907328836154193e-06</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0004432220885064453</v>
+        <v>2.498629783076467e-06</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0009679358918219805</v>
+        <v>9.551218681735918e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0006970454705879092</v>
+        <v>5.85437192057725e-06</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.00137997476849705</v>
+        <v>2.610628143884242e-05</v>
       </c>
       <c r="FS13" t="n">
-        <v>6.945949280634522e-05</v>
+        <v>1.573615372763015e-05</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0002660626778379083</v>
+        <v>6.239503272809088e-05</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0006493350374512374</v>
+        <v>3.825252497335896e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001854190195444971</v>
+        <v>4.353907570475712e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.000627756176982075</v>
+        <v>3.767885209526867e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0003389260964468122</v>
+        <v>2.243151175207458e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0002946047170553356</v>
+        <v>3.237400960642844e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0009633840527385473</v>
+        <v>2.060984661511611e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0002214991836808622</v>
+        <v>1.302203781960998e-05</v>
       </c>
       <c r="GB13" t="n">
-        <v>8.677876758156344e-05</v>
+        <v>6.570178811671212e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.001028981292620301</v>
+        <v>1.768547190295067e-05</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001545144594274461</v>
+        <v>3.656259286799468e-05</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0006669668946415186</v>
+        <v>8.579567293054424e-06</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0001164838613476604</v>
+        <v>2.608295835671015e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>4.945537511957809e-06</v>
+        <v>4.520147922448814e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.144135239883326e-06</v>
+        <v>3.63124163413886e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0004247194156050682</v>
+        <v>0.0002725191006902605</v>
       </c>
       <c r="C14" t="n">
-        <v>7.887799438321963e-05</v>
+        <v>5.17314656462986e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001762864267220721</v>
+        <v>0.0001412053825333714</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0002668102097231895</v>
+        <v>3.825221938313916e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002014251949731261</v>
+        <v>0.000202748051378876</v>
       </c>
       <c r="G14" t="n">
-        <v>7.921770156826824e-05</v>
+        <v>3.258468495914713e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001100318477256224</v>
+        <v>0.0001622035197215155</v>
       </c>
       <c r="I14" t="n">
-        <v>3.230910078855231e-05</v>
+        <v>1.504520696471445e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>4.903999069938436e-06</v>
+        <v>8.397846977459267e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0003251529997214675</v>
+        <v>0.0003807085449807346</v>
       </c>
       <c r="L14" t="n">
-        <v>1.79852268047398e-05</v>
+        <v>3.185319656040519e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001134737831307575</v>
+        <v>0.0002266443334519863</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0002079705009236932</v>
+        <v>0.0001418286265106872</v>
       </c>
       <c r="O14" t="n">
-        <v>0.000195918430108577</v>
+        <v>0.0001983224356081337</v>
       </c>
       <c r="P14" t="n">
-        <v>8.533387881470844e-05</v>
+        <v>7.884683145675808e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.492478779458907e-05</v>
+        <v>5.199751831241883e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.629837738117203e-05</v>
+        <v>5.210960807744414e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>5.730226348532597e-06</v>
+        <v>4.488425474846736e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>7.144099799916148e-05</v>
+        <v>2.774319182208274e-05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.009912466543028e-05</v>
+        <v>3.68037581210956e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>5.840662197442725e-05</v>
+        <v>1.559987140353769e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>4.903901208308525e-05</v>
+        <v>4.856502073380398e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>7.049219129839912e-05</v>
+        <v>1.862282988440711e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.532710823288653e-05</v>
+        <v>4.26326078013517e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.281628182274289e-05</v>
+        <v>3.37284327542875e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.047526479349472e-05</v>
+        <v>2.66461956925923e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.558073174441233e-05</v>
+        <v>6.343134009512141e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.261312228161842e-05</v>
+        <v>7.611150795128196e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.156281415314879e-06</v>
+        <v>2.001460597966798e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.432932135183364e-05</v>
+        <v>3.043211108888499e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.523613173048943e-05</v>
+        <v>7.434921280946583e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.100556932622567e-05</v>
+        <v>7.722813279542606e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.043735680170357e-05</v>
+        <v>1.580261596245691e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.865081427851692e-05</v>
+        <v>6.489341467386112e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.238335117814131e-06</v>
+        <v>2.136983857781161e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.912545096478425e-05</v>
+        <v>4.114941475563683e-06</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.378769755130634e-05</v>
+        <v>7.224393357319059e-06</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.720271474274341e-07</v>
+        <v>2.782584851956926e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.580961907166056e-05</v>
+        <v>2.030483301496133e-07</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.023613913275767e-05</v>
+        <v>5.895632784813643e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.488536357413977e-05</v>
+        <v>5.179374420549721e-05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.346679245121777e-06</v>
+        <v>5.754547601100057e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.950765676563606e-05</v>
+        <v>9.281172970077023e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.432847345015034e-05</v>
+        <v>2.74588746833615e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.860055221593939e-05</v>
+        <v>5.368485653889365e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0002843094698619097</v>
+        <v>0.0002831870515365154</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.668456651619636e-05</v>
+        <v>2.365178261243273e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.238945282646455e-05</v>
+        <v>5.463738852995448e-05</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0001121462701121345</v>
+        <v>0.0001261731958948076</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0001403058122377843</v>
+        <v>0.0001426147646270692</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.395013259752886e-05</v>
+        <v>5.270866495266091e-06</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.867064803373069e-05</v>
+        <v>4.07315701522748e-06</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.621017145225778e-05</v>
+        <v>4.406046355143189e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03069451142801e-05</v>
+        <v>4.456502210814506e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.203295197337866e-05</v>
+        <v>4.241568967700005e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.039233994670212e-05</v>
+        <v>2.851468343578745e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.840794958407059e-05</v>
+        <v>5.039842653786764e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0001745302579365671</v>
+        <v>2.584327739896253e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.390792699065059e-05</v>
+        <v>4.141472891205922e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>7.056917092995718e-05</v>
+        <v>2.240728827018756e-05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>5.555052484851331e-05</v>
+        <v>0.0001293172826990485</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.519765257602558e-05</v>
+        <v>3.086451761191711e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.958340180863161e-05</v>
+        <v>4.935203469358385e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.574875780846924e-05</v>
+        <v>6.439255230361596e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.345184788689949e-05</v>
+        <v>8.631154742033686e-06</v>
       </c>
       <c r="BO14" t="n">
-        <v>7.98931341705611e-06</v>
+        <v>6.380352715495974e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.117483225243632e-05</v>
+        <v>9.486398630542681e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.080290818819776e-05</v>
+        <v>1.679992237768602e-05</v>
       </c>
       <c r="BR14" t="n">
-        <v>2.644135565788019e-05</v>
+        <v>4.68653452116996e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.551536999817472e-05</v>
+        <v>2.878445047826972e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>2.978403608722147e-05</v>
+        <v>2.308065086253919e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.429173011681996e-05</v>
+        <v>3.964411007473245e-05</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0001781567989382893</v>
+        <v>0.0001209993206430227</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.935660636983812e-05</v>
+        <v>1.226399217557628e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>4.173601701040752e-05</v>
+        <v>3.323513737996109e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.465222734026611e-05</v>
+        <v>1.606497244210914e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.337911271548364e-05</v>
+        <v>3.154194564558566e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.794016679923516e-05</v>
+        <v>5.627037899103016e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.296260026923846e-05</v>
+        <v>3.45101288985461e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.960658093797974e-05</v>
+        <v>2.783268610073719e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.632517629943322e-06</v>
+        <v>9.216394573741127e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>6.798426329623908e-05</v>
+        <v>6.830296479165554e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.290404336235952e-05</v>
+        <v>1.572703513375018e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.283534533693455e-05</v>
+        <v>1.495747710578144e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.318295107921585e-05</v>
+        <v>2.660612517502159e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>4.231419006828219e-05</v>
+        <v>3.627585829235613e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.810072353691794e-05</v>
+        <v>2.639157173689455e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.234005048900144e-05</v>
+        <v>7.320059921767097e-06</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.548458749311976e-05</v>
+        <v>4.70189843326807e-06</v>
       </c>
       <c r="CM14" t="n">
-        <v>6.054488767404109e-05</v>
+        <v>3.693684266181663e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>3.751268195628654e-06</v>
+        <v>0.0001503330277046189</v>
       </c>
       <c r="CO14" t="n">
-        <v>7.382400326605421e-06</v>
+        <v>5.447008152259514e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>5.312388566380832e-06</v>
+        <v>7.125046522560297e-06</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.156754115072545e-05</v>
+        <v>3.55357497028308e-06</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.97346817003563e-05</v>
+        <v>7.15224723535357e-06</v>
       </c>
       <c r="CS14" t="n">
-        <v>7.367920625256374e-05</v>
+        <v>1.093632090487517e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>6.404734449461102e-05</v>
+        <v>2.1707692212658e-06</v>
       </c>
       <c r="CU14" t="n">
-        <v>3.776762241614051e-06</v>
+        <v>8.240514944191091e-06</v>
       </c>
       <c r="CV14" t="n">
-        <v>4.697745680459775e-06</v>
+        <v>2.34539074881468e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>5.333154331310652e-05</v>
+        <v>7.765858754282817e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>2.93856155622052e-05</v>
+        <v>1.254289145435905e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>4.764420737046748e-05</v>
+        <v>2.440924072288908e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>7.632856068084948e-06</v>
+        <v>6.516406756418291e-07</v>
       </c>
       <c r="DA14" t="n">
-        <v>5.718956163036637e-05</v>
+        <v>4.498089401749894e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.258692827832419e-05</v>
+        <v>1.783746120054275e-05</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.102286089211702e-05</v>
+        <v>1.955941115738824e-07</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.320259798376355e-06</v>
+        <v>9.522091204416938e-06</v>
       </c>
       <c r="DE14" t="n">
-        <v>3.214063326595351e-05</v>
+        <v>1.385536324960412e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>9.27834480535239e-05</v>
+        <v>6.866813055239618e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.101228735933546e-05</v>
+        <v>0.0001359833695460111</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0001012304710457101</v>
+        <v>4.202255149721168e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>2.892127122322563e-05</v>
+        <v>2.778623456833884e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>6.17704245087225e-06</v>
+        <v>8.506569429300725e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.045502959750593e-05</v>
+        <v>2.085049709421583e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>4.192654159851372e-05</v>
+        <v>1.106915442505851e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>4.302990782889538e-05</v>
+        <v>3.457580532995053e-06</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.302293094340712e-05</v>
+        <v>1.188653550343588e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.453538218105678e-05</v>
+        <v>7.63641728553921e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>8.925667316361796e-06</v>
+        <v>1.697210450402054e-06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>4.688721674028784e-05</v>
+        <v>5.860400415258482e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>1.532076930743642e-05</v>
+        <v>2.885762296500616e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>6.038781066308729e-05</v>
+        <v>3.851549263345078e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>2.541182402637787e-05</v>
+        <v>3.701923560583964e-06</v>
       </c>
       <c r="DU14" t="n">
-        <v>2.316040263394825e-05</v>
+        <v>1.068520396074746e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>1.588164559507277e-05</v>
+        <v>4.298023122828454e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>3.489976734272204e-07</v>
+        <v>4.029432602692395e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>6.429270797525533e-06</v>
+        <v>3.295393253210932e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.353262920631096e-05</v>
+        <v>5.48143834748771e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.035277819028124e-06</v>
+        <v>1.723365312500391e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>2.992536064994056e-05</v>
+        <v>3.853856105706654e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.609467628644779e-05</v>
+        <v>3.91878311347682e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>4.011549208371434e-07</v>
+        <v>1.982237699849065e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>4.052298027090728e-05</v>
+        <v>7.827499211998656e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>1.364006857329514e-05</v>
+        <v>4.791744868271053e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>3.874164758599363e-05</v>
+        <v>2.951399437733926e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>4.769870429299772e-05</v>
+        <v>1.129600696003763e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>3.558797834557481e-05</v>
+        <v>6.735713213856798e-06</v>
       </c>
       <c r="EI14" t="n">
-        <v>2.14052852243185e-05</v>
+        <v>9.659576608100906e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>3.240238584112376e-05</v>
+        <v>2.441835385980085e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.380908335908316e-05</v>
+        <v>4.958789577358402e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>2.731058157223742e-05</v>
+        <v>2.872927780117607e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>6.386806035152404e-06</v>
+        <v>2.503365431039128e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>4.326419457356678e-06</v>
+        <v>8.176322808139957e-06</v>
       </c>
       <c r="EO14" t="n">
-        <v>1.584657002240419e-05</v>
+        <v>5.420714660431258e-05</v>
       </c>
       <c r="EP14" t="n">
-        <v>1.795933167159092e-05</v>
+        <v>2.244024653919041e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>5.692361446563154e-05</v>
+        <v>1.509353478468256e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>4.621267362381332e-05</v>
+        <v>1.94826461665798e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>2.351759030716494e-05</v>
+        <v>3.220081634935923e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>5.046898877480999e-05</v>
+        <v>7.085434390319278e-06</v>
       </c>
       <c r="EU14" t="n">
-        <v>2.057822894130368e-05</v>
+        <v>2.979701639560517e-05</v>
       </c>
       <c r="EV14" t="n">
-        <v>5.251662514638156e-05</v>
+        <v>1.188883470604196e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>8.05621766630793e-06</v>
+        <v>2.851954832294723e-06</v>
       </c>
       <c r="EX14" t="n">
-        <v>1.222914397658315e-05</v>
+        <v>9.010096619022079e-06</v>
       </c>
       <c r="EY14" t="n">
-        <v>5.13975573994685e-05</v>
+        <v>8.253561827586964e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>1.757462450768799e-05</v>
+        <v>2.183395736210514e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>4.595228892867453e-05</v>
+        <v>1.105790943256579e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>5.230128863331629e-07</v>
+        <v>6.494418357760878e-06</v>
       </c>
       <c r="FC14" t="n">
-        <v>4.850561526836827e-05</v>
+        <v>3.3922704460565e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>2.605691952339839e-05</v>
+        <v>2.059223334072158e-07</v>
       </c>
       <c r="FE14" t="n">
-        <v>2.199413574999198e-05</v>
+        <v>6.729537744831759e-06</v>
       </c>
       <c r="FF14" t="n">
-        <v>2.035747093032114e-05</v>
+        <v>9.640489224693738e-06</v>
       </c>
       <c r="FG14" t="n">
-        <v>4.808925950783305e-06</v>
+        <v>1.736001468088944e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>3.958619345212355e-05</v>
+        <v>3.039241346414201e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>3.748705057660118e-05</v>
+        <v>9.561003935232293e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>5.647804937325418e-05</v>
+        <v>1.895962122944184e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>1.697178959148005e-05</v>
+        <v>6.301593384705484e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>3.938442750950344e-05</v>
+        <v>4.136168172408361e-06</v>
       </c>
       <c r="FM14" t="n">
-        <v>1.942671406141017e-05</v>
+        <v>3.310521424282342e-05</v>
       </c>
       <c r="FN14" t="n">
-        <v>3.218322672182694e-05</v>
+        <v>2.888574726966908e-06</v>
       </c>
       <c r="FO14" t="n">
-        <v>3.869440843118355e-05</v>
+        <v>7.159221422625706e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>2.173497159674298e-05</v>
+        <v>4.293422898626886e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>4.738073403132148e-05</v>
+        <v>1.241150948771974e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>2.161208794859704e-05</v>
+        <v>3.95922725147102e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>8.37217885418795e-05</v>
+        <v>0.0001072358354576863</v>
       </c>
       <c r="FT14" t="n">
-        <v>6.472474342444912e-05</v>
+        <v>7.670700142625719e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>9.408029654878192e-06</v>
+        <v>9.911431698128581e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>2.89709132630378e-05</v>
+        <v>8.754341979511082e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>2.791450606309809e-05</v>
+        <v>9.835512901190668e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>1.119237640523352e-05</v>
+        <v>7.555383945145877e-06</v>
       </c>
       <c r="FY14" t="n">
-        <v>5.820060323458165e-05</v>
+        <v>2.807609598676208e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>7.917844868643442e-07</v>
+        <v>7.449894837918691e-06</v>
       </c>
       <c r="GA14" t="n">
-        <v>2.4302191377501e-05</v>
+        <v>2.707145540625788e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>4.577270374284126e-05</v>
+        <v>2.78480292763561e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>4.58371068816632e-05</v>
+        <v>1.674211853242014e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>5.692778358934447e-05</v>
+        <v>3.782503699767403e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0001493427553214133</v>
+        <v>4.828255987376906e-05</v>
       </c>
       <c r="GF14" t="n">
-        <v>1.021136267809197e-05</v>
+        <v>1.276537568628555e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>2.052039235422853e-05</v>
+        <v>2.568702620919794e-05</v>
       </c>
     </row>
     <row r="15">
